--- a/knto_images(현황).xlsx
+++ b/knto_images(현황).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\WebImages_travel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFEAD33D-859A-447E-AF14-0F668E892AF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBE3748-BFE5-4142-B6BA-F8911426B1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3128" yWindow="0" windowWidth="17865" windowHeight="12780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3983" yWindow="0" windowWidth="17865" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="전체" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="129">
   <si>
     <t>여행지명</t>
   </si>
@@ -40,367 +40,498 @@
     <t>순천만국가정원</t>
   </si>
   <si>
-    <t>하이커 그라운드</t>
+    <t>중문골프장</t>
+  </si>
+  <si>
+    <t>보은 법주사</t>
+  </si>
+  <si>
+    <t>수덕사</t>
+  </si>
+  <si>
+    <t>봉수산 수목원</t>
+  </si>
+  <si>
+    <t>외암민속마을</t>
+  </si>
+  <si>
+    <t>카멜리아힐</t>
+  </si>
+  <si>
+    <t>밀양 영남루</t>
+  </si>
+  <si>
+    <t>내소사</t>
+  </si>
+  <si>
+    <t>부안청자박물관</t>
+  </si>
+  <si>
+    <t>달빛쌈지공원</t>
+  </si>
+  <si>
+    <t>예산황새공원</t>
+  </si>
+  <si>
+    <t>1100고지습지</t>
+  </si>
+  <si>
+    <t>함덕 서우봉해변</t>
+  </si>
+  <si>
+    <t>순천 낙안읍성</t>
+  </si>
+  <si>
+    <t>정약용유적지</t>
+  </si>
+  <si>
+    <t>수성당</t>
+  </si>
+  <si>
+    <t>제주허브동산</t>
+  </si>
+  <si>
+    <t>말티재 전망대</t>
+  </si>
+  <si>
+    <t>밀양 트윈터널</t>
+  </si>
+  <si>
+    <t>학 전망대</t>
+  </si>
+  <si>
+    <t>보은 삼년산성</t>
+  </si>
+  <si>
+    <t>성읍녹차마을</t>
+  </si>
+  <si>
+    <t>만휴정</t>
+  </si>
+  <si>
+    <t>부안 솔섬</t>
+  </si>
+  <si>
+    <t>경희궁</t>
+  </si>
+  <si>
+    <t>철원향교</t>
+  </si>
+  <si>
+    <t>협재해수욕장</t>
+  </si>
+  <si>
+    <t>명동거리</t>
+  </si>
+  <si>
+    <t>철원 도피안사</t>
+  </si>
+  <si>
+    <t>하도해수욕장</t>
+  </si>
+  <si>
+    <t>고석정국민관광지</t>
+  </si>
+  <si>
+    <t>경복궁</t>
+  </si>
+  <si>
+    <t>쇠소깍</t>
+  </si>
+  <si>
+    <t>안동시립민속박물관</t>
+  </si>
+  <si>
+    <t>월정리해수욕장</t>
+  </si>
+  <si>
+    <t>격포해수욕장</t>
+  </si>
+  <si>
+    <t>계화도</t>
+  </si>
+  <si>
+    <t>밀양 금시당 백곡재</t>
+  </si>
+  <si>
+    <t>웅도</t>
+  </si>
+  <si>
+    <t>밀양 관아지</t>
+  </si>
+  <si>
+    <t>익선동 한옥거리</t>
+  </si>
+  <si>
+    <t>다산생태공원</t>
+  </si>
+  <si>
+    <t>서울남산</t>
+  </si>
+  <si>
+    <t>철원 한탄강 은하수교</t>
+  </si>
+  <si>
+    <t>창덕궁</t>
+  </si>
+  <si>
+    <t>김녕성세기해변</t>
+  </si>
+  <si>
+    <t>경천대 국민관광지</t>
+  </si>
+  <si>
+    <t>예산 카페</t>
+  </si>
+  <si>
+    <t>적벽강</t>
+  </si>
+  <si>
+    <t>크룽지</t>
+  </si>
+  <si>
+    <t>표선해수욕장</t>
+  </si>
+  <si>
+    <t>덕수궁</t>
+  </si>
+  <si>
+    <t>간월암</t>
+  </si>
+  <si>
+    <t>상주곶감공원</t>
+  </si>
+  <si>
+    <t>북한강 철교</t>
+  </si>
+  <si>
+    <t>철원 노동당사</t>
+  </si>
+  <si>
+    <t>이호테우해변</t>
+  </si>
+  <si>
+    <t>철원관광정보센터</t>
+  </si>
+  <si>
+    <t>코난해변</t>
+  </si>
+  <si>
+    <t>서산 해미읍성</t>
+  </si>
+  <si>
+    <t>월영교</t>
+  </si>
+  <si>
+    <t>광화문</t>
+  </si>
+  <si>
+    <t>신창풍차해안도로</t>
+  </si>
+  <si>
+    <t>안동구시장</t>
+  </si>
+  <si>
+    <t>안동문화관광단지</t>
+  </si>
+  <si>
+    <t>격포항</t>
+  </si>
+  <si>
+    <t>천지연폭포</t>
+  </si>
+  <si>
+    <t>채석강</t>
+  </si>
+  <si>
+    <t>창경궁</t>
+  </si>
+  <si>
+    <t>두물머리</t>
+  </si>
+  <si>
+    <t>경천섬공원</t>
+  </si>
+  <si>
+    <t>위양못</t>
+  </si>
+  <si>
+    <t>월정투명카약</t>
+  </si>
+  <si>
+    <t>정이품송</t>
+  </si>
+  <si>
+    <t>밀양읍성</t>
+  </si>
+  <si>
+    <t>만어사</t>
+  </si>
+  <si>
+    <t>안동하회마을</t>
+  </si>
+  <si>
+    <t>아그로랜드 태신목장</t>
+  </si>
+  <si>
+    <t>청풍호반케이블카</t>
+  </si>
+  <si>
+    <t>상주 도남서원</t>
+  </si>
+  <si>
+    <t>낙강교</t>
+  </si>
+  <si>
+    <t>삼부연폭포</t>
+  </si>
+  <si>
+    <t>수풀로 양수리</t>
+  </si>
+  <si>
+    <t>순천만습지</t>
+  </si>
+  <si>
+    <t>금능해수욕장</t>
+  </si>
+  <si>
+    <t>직탕폭포</t>
+  </si>
+  <si>
+    <t>경복궁 수문장 교대의식</t>
+  </si>
+  <si>
+    <t>병산서원</t>
+  </si>
+  <si>
+    <t>성산일출봉</t>
+  </si>
+  <si>
+    <t>유아숲체험원</t>
+  </si>
+  <si>
+    <t>국립현대미술관덕수궁관</t>
+  </si>
+  <si>
+    <t>부용대</t>
+  </si>
+  <si>
+    <t>퍼플섬</t>
+  </si>
+  <si>
+    <t>국립현대미술관</t>
+  </si>
+  <si>
+    <t xml:space="preserve">경희궁: 3월 경희궁 봄 산책 가이드 (꽃 피는 길목 추천, 역사 스토리, 입장료 팁)  </t>
+  </si>
+  <si>
+    <t>경희궁: 경희궁에서 만나는 3월의 고즈넉한 매력 (봄 행사 일정, 주변 카페 추천, 사진 촬영 포인트)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">명동거리: 3월 명동거리 쇼핑 &amp; 먹거리 투어 (봄 세일 정보, 스트리트 푸드 베스트, 교통 팁)  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">경복궁: 3월 경복궁 한복 대여 &amp; 궁궐 탐방 (봄꽃 배경 사진 팁, 입장 시간대 추천, 역사 해설)  </t>
+  </si>
+  <si>
+    <t>경복궁: 경복궁 3월 특별 행사와 방문 팁 (수문장 교대식 일정, 주변 산책로, 주차 정보)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">익선동 한옥거리: 3월 익선동 한옥거리 카페 탐방 (봄 분위기 카페 추천, 한옥 골목 산책 코스, 음식 메뉴 팁)  </t>
+  </si>
+  <si>
+    <t>익선동 한옥거리: 익선동에서 느끼는 3월의 레트로 감성 (사진 명소, 주변 상점 가이드, 방문 시간 추천)</t>
+  </si>
+  <si>
+    <t>서울남산: 서울남산 3월 야경과 데이트 스팟 (N서울타워 이벤트, 주변 레스토랑 추천, 교통 팁)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">창덕궁: 3월 창덕궁 비밀의 정원 봄 탐험 (후원 입장 예약 팁, 꽃 피는 정원 가이드, 역사 이야기)  </t>
+  </si>
+  <si>
+    <t>창덕궁: 창덕궁에서 즐기는 3월 궁궐 피크닉 (봄 행사 일정, 주변 편의시설, 사진 촬영 팁)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">덕수궁: 3월 덕수궁 석조전과 봄 산책 (야간 개장 정보, 역사 전시 추천, 입장 팁)  </t>
+  </si>
+  <si>
+    <t>덕수궁: 덕수궁 3월 문화 행사와 주변 투어 (콘서트 일정, 카페 추천, 교통 가이드)</t>
+  </si>
+  <si>
+    <t>광화문: 광화문에서 만나는 3월 서울의 심장 (역사 산책 코스, 푸드트럭 팁, 방문 시간 추천)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">창경궁: 3월 창경궁 온실과 봄꽃 만개 (온실 투어 가이드, 궁궐 이벤트, 입장료 정보)  </t>
+  </si>
+  <si>
+    <t>창경궁: 창경궁 3월 야간 관람 팁과 매력 (조명 행사 일정, 주변 산책로, 사진 촬영 스팟)</t>
+  </si>
+  <si>
+    <t>수문장 교대의식: 수문장 교대의식과 함께하는 3월 궁궐 데이트 (의상 설명, 사진 팁, 입장 정보)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">국립현대미술관: 3월 국립현대미술관 봄 전시 추천 (특별전 일정, 관람 팁, 카페 휴식)  </t>
+  </si>
+  <si>
+    <t>국립현대미술관: 국립현대미술관에서 즐기는 3월 문화 데이 (작품 해설, 주변 산책 코스, 티켓 예매 가이드)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">광화문: 3월 광화문 광장 봄 축제 즐기기 (이벤트 스케줄, 주변 명소 연계, 사진 포인트)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">수문장 교대의식: 3월 수문장 교대의식 관람 가이드 (공연 시간표, 베스트 뷰 포인트, 주변 궁궐 연계)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3.3 추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뚝섬전망문화콤플렉스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">서울남산: 3월 서울남산 케이블카 &amp; 전망대 힐링 (봄 벚꽃 뷰 포인트, 산책 트레일, 입장료 정보)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>명동거리: 봄바람 타고 즐기는 3월 명동거리 데이트 코스 (화장품 쇼핑 가이드, 카페 휴식 스팟, 밤 야경 추천)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>롯데월드타워</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>코엑스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>하이커</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>그라운드</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>속리산테마파크</t>
-  </si>
-  <si>
-    <t>양평 양떼목장</t>
-  </si>
-  <si>
-    <t>철원 한탄강 주상절리길</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양평</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>양떼목장</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>철원</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>한탄강</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>주상절리길</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>들꽃수목원</t>
-  </si>
-  <si>
-    <t>중문골프장</t>
-  </si>
-  <si>
-    <t>보은 법주사</t>
-  </si>
-  <si>
-    <t>수덕사</t>
-  </si>
-  <si>
-    <t>봉수산 수목원</t>
-  </si>
-  <si>
-    <t>외암민속마을</t>
-  </si>
-  <si>
-    <t>카멜리아힐</t>
-  </si>
-  <si>
-    <t>밀양 영남루</t>
-  </si>
-  <si>
-    <t>내소사</t>
-  </si>
-  <si>
-    <t>부안청자박물관</t>
-  </si>
-  <si>
-    <t>달빛쌈지공원</t>
-  </si>
-  <si>
-    <t>예산황새공원</t>
-  </si>
-  <si>
-    <t>1100고지습지</t>
-  </si>
-  <si>
-    <t>함덕 서우봉해변</t>
-  </si>
-  <si>
-    <t>순천 낙안읍성</t>
-  </si>
-  <si>
-    <t>정약용유적지</t>
-  </si>
-  <si>
-    <t>수성당</t>
-  </si>
-  <si>
-    <t>제주허브동산</t>
-  </si>
-  <si>
-    <t>말티재 전망대</t>
-  </si>
-  <si>
-    <t>밀양 트윈터널</t>
-  </si>
-  <si>
-    <t>학 전망대</t>
-  </si>
-  <si>
-    <t>보은 삼년산성</t>
-  </si>
-  <si>
-    <t>성읍녹차마을</t>
-  </si>
-  <si>
-    <t>만휴정</t>
-  </si>
-  <si>
-    <t>부안 솔섬</t>
-  </si>
-  <si>
-    <t>경희궁</t>
-  </si>
-  <si>
-    <t>철원향교</t>
-  </si>
-  <si>
-    <t>협재해수욕장</t>
-  </si>
-  <si>
-    <t>명동거리</t>
-  </si>
-  <si>
-    <t>철원 도피안사</t>
-  </si>
-  <si>
-    <t>하도해수욕장</t>
-  </si>
-  <si>
-    <t>고석정국민관광지</t>
-  </si>
-  <si>
-    <t>경복궁</t>
-  </si>
-  <si>
-    <t>쇠소깍</t>
-  </si>
-  <si>
-    <t>안동시립민속박물관</t>
-  </si>
-  <si>
-    <t>월정리해수욕장</t>
-  </si>
-  <si>
-    <t>격포해수욕장</t>
-  </si>
-  <si>
-    <t>계화도</t>
-  </si>
-  <si>
-    <t>밀양 금시당 백곡재</t>
-  </si>
-  <si>
-    <t>웅도</t>
-  </si>
-  <si>
-    <t>밀양 관아지</t>
-  </si>
-  <si>
-    <t>익선동 한옥거리</t>
-  </si>
-  <si>
-    <t>다산생태공원</t>
-  </si>
-  <si>
-    <t>서울남산</t>
-  </si>
-  <si>
-    <t>철원 한탄강 은하수교</t>
-  </si>
-  <si>
-    <t>창덕궁</t>
-  </si>
-  <si>
-    <t>김녕성세기해변</t>
-  </si>
-  <si>
-    <t>경천대 국민관광지</t>
-  </si>
-  <si>
-    <t>예산 카페</t>
-  </si>
-  <si>
-    <t>적벽강</t>
-  </si>
-  <si>
-    <t>크룽지</t>
-  </si>
-  <si>
-    <t>표선해수욕장</t>
-  </si>
-  <si>
-    <t>덕수궁</t>
-  </si>
-  <si>
-    <t>간월암</t>
-  </si>
-  <si>
-    <t>상주곶감공원</t>
-  </si>
-  <si>
-    <t>북한강 철교</t>
-  </si>
-  <si>
-    <t>철원 노동당사</t>
-  </si>
-  <si>
-    <t>이호테우해변</t>
-  </si>
-  <si>
-    <t>철원관광정보센터</t>
-  </si>
-  <si>
-    <t>코난해변</t>
-  </si>
-  <si>
-    <t>서산 해미읍성</t>
-  </si>
-  <si>
-    <t>월영교</t>
-  </si>
-  <si>
-    <t>광화문</t>
-  </si>
-  <si>
-    <t>신창풍차해안도로</t>
-  </si>
-  <si>
-    <t>안동구시장</t>
-  </si>
-  <si>
-    <t>안동문화관광단지</t>
-  </si>
-  <si>
-    <t>격포항</t>
-  </si>
-  <si>
-    <t>천지연폭포</t>
-  </si>
-  <si>
-    <t>채석강</t>
-  </si>
-  <si>
-    <t>창경궁</t>
-  </si>
-  <si>
-    <t>두물머리</t>
-  </si>
-  <si>
-    <t>경천섬공원</t>
-  </si>
-  <si>
-    <t>위양못</t>
-  </si>
-  <si>
-    <t>월정투명카약</t>
-  </si>
-  <si>
-    <t>정이품송</t>
-  </si>
-  <si>
-    <t>밀양읍성</t>
-  </si>
-  <si>
-    <t>만어사</t>
-  </si>
-  <si>
-    <t>안동하회마을</t>
-  </si>
-  <si>
-    <t>아그로랜드 태신목장</t>
-  </si>
-  <si>
-    <t>청풍호반케이블카</t>
-  </si>
-  <si>
-    <t>상주 도남서원</t>
-  </si>
-  <si>
-    <t>낙강교</t>
-  </si>
-  <si>
-    <t>삼부연폭포</t>
-  </si>
-  <si>
-    <t>수풀로 양수리</t>
-  </si>
-  <si>
-    <t>순천만습지</t>
-  </si>
-  <si>
-    <t>금능해수욕장</t>
-  </si>
-  <si>
-    <t>직탕폭포</t>
-  </si>
-  <si>
-    <t>경복궁 수문장 교대의식</t>
-  </si>
-  <si>
-    <t>병산서원</t>
-  </si>
-  <si>
-    <t>성산일출봉</t>
-  </si>
-  <si>
-    <t>유아숲체험원</t>
-  </si>
-  <si>
-    <t>국립현대미술관덕수궁관</t>
-  </si>
-  <si>
-    <t>부용대</t>
-  </si>
-  <si>
-    <t>퍼플섬</t>
-  </si>
-  <si>
-    <t>국립현대미술관</t>
-  </si>
-  <si>
-    <t xml:space="preserve">경희궁: 3월 경희궁 봄 산책 가이드 (꽃 피는 길목 추천, 역사 스토리, 입장료 팁)  </t>
-  </si>
-  <si>
-    <t>경희궁: 경희궁에서 만나는 3월의 고즈넉한 매력 (봄 행사 일정, 주변 카페 추천, 사진 촬영 포인트)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">명동거리: 3월 명동거리 쇼핑 &amp; 먹거리 투어 (봄 세일 정보, 스트리트 푸드 베스트, 교통 팁)  </t>
-  </si>
-  <si>
-    <t>명동거리: 봄바람 타고 즐기는 3월 명동거리 데이트 코스 (화장품 쇼핑 가이드, 카페 휴식 스팟, 밤 야경 추천)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">경복궁: 3월 경복궁 한복 대여 &amp; 궁궐 탐방 (봄꽃 배경 사진 팁, 입장 시간대 추천, 역사 해설)  </t>
-  </si>
-  <si>
-    <t>경복궁: 경복궁 3월 특별 행사와 방문 팁 (수문장 교대식 일정, 주변 산책로, 주차 정보)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">익선동 한옥거리: 3월 익선동 한옥거리 카페 탐방 (봄 분위기 카페 추천, 한옥 골목 산책 코스, 음식 메뉴 팁)  </t>
-  </si>
-  <si>
-    <t>익선동 한옥거리: 익선동에서 느끼는 3월의 레트로 감성 (사진 명소, 주변 상점 가이드, 방문 시간 추천)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">서울남산: 3월 서울남산 케이블카 &amp; 전망대 힐링 (봄 벚꽃 뷰 포인트, 산책 트레일, 입장료 정보)  </t>
-  </si>
-  <si>
-    <t>서울남산: 서울남산 3월 야경과 데이트 스팟 (N서울타워 이벤트, 주변 레스토랑 추천, 교통 팁)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">창덕궁: 3월 창덕궁 비밀의 정원 봄 탐험 (후원 입장 예약 팁, 꽃 피는 정원 가이드, 역사 이야기)  </t>
-  </si>
-  <si>
-    <t>창덕궁: 창덕궁에서 즐기는 3월 궁궐 피크닉 (봄 행사 일정, 주변 편의시설, 사진 촬영 팁)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">덕수궁: 3월 덕수궁 석조전과 봄 산책 (야간 개장 정보, 역사 전시 추천, 입장 팁)  </t>
-  </si>
-  <si>
-    <t>덕수궁: 덕수궁 3월 문화 행사와 주변 투어 (콘서트 일정, 카페 추천, 교통 가이드)</t>
-  </si>
-  <si>
-    <t>광화문: 광화문에서 만나는 3월 서울의 심장 (역사 산책 코스, 푸드트럭 팁, 방문 시간 추천)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">창경궁: 3월 창경궁 온실과 봄꽃 만개 (온실 투어 가이드, 궁궐 이벤트, 입장료 정보)  </t>
-  </si>
-  <si>
-    <t>창경궁: 창경궁 3월 야간 관람 팁과 매력 (조명 행사 일정, 주변 산책로, 사진 촬영 스팟)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">수문장 교대의식: 3월 수문장 교대의식 관람 가이드 (공연 시간표, 베스트 뷰 포인트, 주변 궁궐 연계)  </t>
-  </si>
-  <si>
-    <t>수문장 교대의식: 수문장 교대의식과 함께하는 3월 궁궐 데이트 (의상 설명, 사진 팁, 입장 정보)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">국립현대미술관: 3월 국립현대미술관 봄 전시 추천 (특별전 일정, 관람 팁, 카페 휴식)  </t>
-  </si>
-  <si>
-    <t>국립현대미술관: 국립현대미술관에서 즐기는 3월 문화 데이 (작품 해설, 주변 산책 코스, 티켓 예매 가이드)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광화문: 3월 광화문 광장 봄 축제 즐기기 (이벤트 스케줄, 주변 명소 연계, 사진 포인트)  </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -408,7 +539,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -435,8 +566,22 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -455,6 +600,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -468,7 +625,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -479,6 +636,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -783,52 +949,52 @@
         <v>2</v>
       </c>
       <c r="C2" s="2">
-        <v>112</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B3" s="2" t="s">
-        <v>3</v>
+      <c r="B3" s="9" t="s">
+        <v>124</v>
       </c>
       <c r="C3" s="2">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B4" s="2" t="s">
-        <v>4</v>
+      <c r="B4" s="10" t="s">
+        <v>125</v>
       </c>
       <c r="C4" s="2">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B5" s="2" t="s">
-        <v>5</v>
+      <c r="B5" s="9" t="s">
+        <v>126</v>
       </c>
       <c r="C5" s="2">
-        <v>34</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="9" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="B7" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="C7" s="2">
         <v>6</v>
-      </c>
-      <c r="C6" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="2">
-        <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B8" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="C8" s="2">
         <v>28</v>
@@ -836,7 +1002,7 @@
     </row>
     <row r="9" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C9" s="2">
         <v>25</v>
@@ -844,7 +1010,7 @@
     </row>
     <row r="10" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B10" s="2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C10" s="2">
         <v>25</v>
@@ -852,7 +1018,7 @@
     </row>
     <row r="11" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B11" s="2" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C11" s="2">
         <v>23</v>
@@ -860,7 +1026,7 @@
     </row>
     <row r="12" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B12" s="2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C12" s="2">
         <v>22</v>
@@ -868,7 +1034,7 @@
     </row>
     <row r="13" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B13" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2">
         <v>21</v>
@@ -876,7 +1042,7 @@
     </row>
     <row r="14" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B14" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C14" s="2">
         <v>21</v>
@@ -884,7 +1050,7 @@
     </row>
     <row r="15" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B15" s="2" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2">
         <v>19</v>
@@ -892,7 +1058,7 @@
     </row>
     <row r="16" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C16" s="2">
         <v>17</v>
@@ -900,7 +1066,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B17" s="2" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C17" s="2">
         <v>15</v>
@@ -908,7 +1074,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B18" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2">
         <v>15</v>
@@ -916,7 +1082,7 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B19" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C19" s="2">
         <v>14</v>
@@ -924,7 +1090,7 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B20" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C20" s="2">
         <v>14</v>
@@ -932,7 +1098,7 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B21" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C21" s="2">
         <v>13</v>
@@ -940,7 +1106,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B22" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C22" s="2">
         <v>13</v>
@@ -948,7 +1114,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B23" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C23" s="2">
         <v>12</v>
@@ -956,7 +1122,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B24" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C24" s="2">
         <v>11</v>
@@ -964,7 +1130,7 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B25" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C25" s="2">
         <v>11</v>
@@ -972,7 +1138,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B26" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C26" s="2">
         <v>11</v>
@@ -980,7 +1146,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B27" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C27" s="2">
         <v>11</v>
@@ -988,7 +1154,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B28" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C28" s="2">
         <v>11</v>
@@ -996,7 +1162,7 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B29" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C29" s="2">
         <v>10</v>
@@ -1004,7 +1170,7 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B30" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C30" s="2">
         <v>10</v>
@@ -1012,7 +1178,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B31" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C31" s="2">
         <v>9</v>
@@ -1023,7 +1189,7 @@
         <v>1</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C32" s="2">
         <v>9</v>
@@ -1031,7 +1197,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B33" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C33" s="2">
         <v>9</v>
@@ -1039,7 +1205,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B34" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C34" s="2">
         <v>9</v>
@@ -1050,7 +1216,7 @@
         <v>1</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C35" s="2">
         <v>9</v>
@@ -1058,7 +1224,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B36" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C36" s="2">
         <v>9</v>
@@ -1066,7 +1232,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B37" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C37" s="2">
         <v>8</v>
@@ -1074,7 +1240,7 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B38" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C38" s="2">
         <v>8</v>
@@ -1085,7 +1251,7 @@
         <v>1</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C39" s="2">
         <v>8</v>
@@ -1093,7 +1259,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B40" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C40" s="2">
         <v>8</v>
@@ -1101,7 +1267,7 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B41" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C41" s="2">
         <v>8</v>
@@ -1109,7 +1275,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B42" s="2" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C42" s="2">
         <v>8</v>
@@ -1117,7 +1283,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B43" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C43" s="2">
         <v>8</v>
@@ -1125,7 +1291,7 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B44" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C44" s="2">
         <v>8</v>
@@ -1133,7 +1299,7 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B45" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C45" s="2">
         <v>8</v>
@@ -1141,7 +1307,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B46" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C46" s="2">
         <v>7</v>
@@ -1149,7 +1315,7 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B47" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C47" s="2">
         <v>7</v>
@@ -1160,7 +1326,7 @@
         <v>1</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C48" s="2">
         <v>7</v>
@@ -1168,7 +1334,7 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B49" s="2" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C49" s="2">
         <v>7</v>
@@ -1179,7 +1345,7 @@
         <v>1</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C50" s="2">
         <v>7</v>
@@ -1187,7 +1353,7 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B51" s="2" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="C51" s="2">
         <v>6</v>
@@ -1198,7 +1364,7 @@
         <v>1</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C52" s="2">
         <v>6</v>
@@ -1206,7 +1372,7 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B53" s="2" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C53" s="2">
         <v>6</v>
@@ -1214,7 +1380,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B54" s="2" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C54" s="2">
         <v>6</v>
@@ -1222,7 +1388,7 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B55" s="2" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C55" s="2">
         <v>6</v>
@@ -1230,7 +1396,7 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B56" s="2" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C56" s="2">
         <v>6</v>
@@ -1238,7 +1404,7 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B57" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C57" s="2">
         <v>6</v>
@@ -1246,7 +1412,7 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B58" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="C58" s="2">
         <v>6</v>
@@ -1257,7 +1423,7 @@
         <v>1</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C59" s="2">
         <v>6</v>
@@ -1265,7 +1431,7 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B60" s="2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="C60" s="2">
         <v>6</v>
@@ -1273,7 +1439,7 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B61" s="2" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="C61" s="2">
         <v>6</v>
@@ -1281,7 +1447,7 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B62" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C62" s="2">
         <v>6</v>
@@ -1289,7 +1455,7 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B63" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="C63" s="2">
         <v>5</v>
@@ -1297,7 +1463,7 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B64" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C64" s="2">
         <v>5</v>
@@ -1305,7 +1471,7 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B65" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C65" s="2">
         <v>5</v>
@@ -1313,7 +1479,7 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B66" s="2" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="C66" s="2">
         <v>5</v>
@@ -1321,7 +1487,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B67" s="2" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="C67" s="2">
         <v>5</v>
@@ -1329,7 +1495,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B68" s="2" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C68" s="2">
         <v>5</v>
@@ -1340,7 +1506,7 @@
         <v>1</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C69" s="2">
         <v>5</v>
@@ -1348,7 +1514,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B70" s="2" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C70" s="2">
         <v>5</v>
@@ -1356,7 +1522,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B71" s="2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C71" s="2">
         <v>5</v>
@@ -1364,7 +1530,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B72" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C72" s="2">
         <v>5</v>
@@ -1372,7 +1538,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B73" s="2" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="C73" s="2">
         <v>4</v>
@@ -1380,7 +1546,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B74" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="C74" s="2">
         <v>4</v>
@@ -1388,7 +1554,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B75" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C75" s="2">
         <v>4</v>
@@ -1399,7 +1565,7 @@
         <v>1</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C76" s="2">
         <v>4</v>
@@ -1407,7 +1573,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B77" s="2" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C77" s="2">
         <v>4</v>
@@ -1415,7 +1581,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B78" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C78" s="2">
         <v>4</v>
@@ -1423,7 +1589,7 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B79" s="2" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C79" s="2">
         <v>4</v>
@@ -1431,7 +1597,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B80" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C80" s="2">
         <v>4</v>
@@ -1439,7 +1605,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B81" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="C81" s="2">
         <v>4</v>
@@ -1447,7 +1613,7 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B82" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="C82" s="2">
         <v>4</v>
@@ -1455,7 +1621,7 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B83" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C83" s="2">
         <v>3</v>
@@ -1463,7 +1629,7 @@
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B84" s="2" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C84" s="2">
         <v>3</v>
@@ -1471,7 +1637,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B85" s="2" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C85" s="2">
         <v>3</v>
@@ -1479,7 +1645,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B86" s="2" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="C86" s="2">
         <v>2</v>
@@ -1487,7 +1653,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B87" s="2" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C87" s="2">
         <v>2</v>
@@ -1495,7 +1661,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B88" s="2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="C88" s="2">
         <v>2</v>
@@ -1503,7 +1669,7 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B89" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C89" s="2">
         <v>2</v>
@@ -1511,7 +1677,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B90" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="C90" s="2">
         <v>2</v>
@@ -1519,7 +1685,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B91" s="2" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="C91" s="2">
         <v>2</v>
@@ -1527,7 +1693,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B92" s="2" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="C92" s="2">
         <v>2</v>
@@ -1535,7 +1701,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B93" s="2" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="C93" s="2">
         <v>2</v>
@@ -1546,7 +1712,7 @@
         <v>1</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C94" s="2">
         <v>2</v>
@@ -1554,7 +1720,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B95" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="C95" s="2">
         <v>2</v>
@@ -1562,7 +1728,7 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B96" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C96" s="2">
         <v>1</v>
@@ -1570,7 +1736,7 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B97" s="2" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="C97" s="2">
         <v>1</v>
@@ -1581,7 +1747,7 @@
         <v>1</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C98" s="2">
         <v>1</v>
@@ -1589,7 +1755,7 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B99" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C99" s="2">
         <v>1</v>
@@ -1597,7 +1763,7 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.6">
       <c r="B100" s="2" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C100" s="2">
         <v>1</v>
@@ -1608,7 +1774,7 @@
         <v>1</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C101" s="2">
         <v>1</v>
@@ -1648,13 +1814,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C2" s="5">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.6">
@@ -1662,13 +1828,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C3" s="5">
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.6">
@@ -1676,7 +1842,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C4" s="5">
         <v>8</v>
@@ -1688,13 +1854,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C5" s="5">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.6">
@@ -1702,13 +1868,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C6" s="5">
         <v>7</v>
       </c>
-      <c r="F6" t="s">
-        <v>105</v>
+      <c r="F6" s="8" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.6">
@@ -1716,7 +1882,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C7" s="5">
         <v>6</v>
@@ -1728,13 +1894,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="C8" s="5">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.6">
@@ -1742,13 +1908,13 @@
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C9" s="5">
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.6">
@@ -1756,7 +1922,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="C10" s="5">
         <v>4</v>
@@ -1768,13 +1934,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="C11" s="5">
         <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.6">
@@ -1782,13 +1948,13 @@
         <v>1</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="C12" s="5">
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.6">
@@ -1796,757 +1962,421 @@
         <v>1</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C13" s="5">
         <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C14" s="2">
+      <c r="A14" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="B15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="1">
+        <v>6</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.6">
+      <c r="B16" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="C16" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="1">
+        <v>6</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="F18" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="F20" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="F21" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="F23" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="F24" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="F26" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="F27" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="F29" s="7" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="F30" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B15" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C15" s="2">
-        <v>36</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B16" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B17" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C17" s="2">
-        <v>34</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="2">
-        <v>31</v>
-      </c>
-      <c r="F18" s="1" t="s">
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="F32" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B19" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B20" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="2">
-        <v>28</v>
-      </c>
-      <c r="F20" s="1" t="s">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="F33" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B21" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2">
-        <v>25</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B22" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B23" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="2">
-        <v>23</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B24" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C24" s="2">
-        <v>22</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B25" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C25" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B26" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="2">
-        <v>21</v>
-      </c>
-      <c r="F26" s="1" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B27" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C27" s="2">
-        <v>19</v>
-      </c>
-      <c r="F27" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" s="2">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C29" s="2">
-        <v>15</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B30" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="C30" s="2">
-        <v>15</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B31" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="2">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C32" s="2">
-        <v>14</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B33" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" s="2">
-        <v>13</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B34" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" s="2">
-        <v>13</v>
-      </c>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35" s="2">
-        <v>12</v>
-      </c>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B36" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="2">
-        <v>11</v>
-      </c>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B37" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C37" s="2">
-        <v>11</v>
-      </c>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B38" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="C38" s="2">
-        <v>11</v>
-      </c>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B39" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="2">
-        <v>11</v>
-      </c>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B40" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C40" s="2">
-        <v>11</v>
-      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B41" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C41" s="2">
-        <v>10</v>
-      </c>
+      <c r="B41" s="2"/>
+      <c r="C41" s="2"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B42" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C42" s="2">
-        <v>10</v>
-      </c>
+      <c r="B42" s="2"/>
+      <c r="C42" s="2"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B43" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="2">
-        <v>9</v>
-      </c>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B44" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C44" s="2">
-        <v>9</v>
-      </c>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B45" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C45" s="2">
-        <v>9</v>
-      </c>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B46" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C46" s="2">
-        <v>9</v>
-      </c>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B47" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="C47" s="2">
-        <v>8</v>
-      </c>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B48" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="C48" s="2">
-        <v>8</v>
-      </c>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B49" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C49" s="2">
-        <v>8</v>
-      </c>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B50" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="2">
-        <v>8</v>
-      </c>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B51" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C51" s="2">
-        <v>8</v>
-      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B52" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C52" s="2">
-        <v>8</v>
-      </c>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B53" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C53" s="2">
-        <v>8</v>
-      </c>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B54" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C54" s="2">
-        <v>8</v>
-      </c>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B55" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C55" s="2">
-        <v>7</v>
-      </c>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B56" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C56" s="2">
-        <v>7</v>
-      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B57" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C57" s="2">
-        <v>7</v>
-      </c>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B58" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C58" s="2">
-        <v>6</v>
-      </c>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B59" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C59" s="2">
-        <v>6</v>
-      </c>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B60" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C60" s="2">
-        <v>6</v>
-      </c>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B61" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C61" s="2">
-        <v>6</v>
-      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B62" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C62" s="2">
-        <v>6</v>
-      </c>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B63" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C63" s="2">
-        <v>6</v>
-      </c>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B64" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C64" s="2">
-        <v>6</v>
-      </c>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B65" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C65" s="2">
-        <v>6</v>
-      </c>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B66" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C66" s="2">
-        <v>6</v>
-      </c>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B67" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C67" s="2">
-        <v>6</v>
-      </c>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B68" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C68" s="2">
-        <v>5</v>
-      </c>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B69" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C69" s="2">
-        <v>5</v>
-      </c>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B70" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C70" s="2">
-        <v>5</v>
-      </c>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
     </row>
     <row r="71" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B71" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C71" s="2">
-        <v>5</v>
-      </c>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
     </row>
     <row r="72" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B72" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C72" s="2">
-        <v>5</v>
-      </c>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
     </row>
     <row r="73" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B73" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C73" s="2">
-        <v>5</v>
-      </c>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
     </row>
     <row r="74" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B74" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C74" s="2">
-        <v>5</v>
-      </c>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
     </row>
     <row r="75" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B75" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C75" s="2">
-        <v>5</v>
-      </c>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
     </row>
     <row r="76" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B76" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C76" s="2">
-        <v>5</v>
-      </c>
+      <c r="B76" s="2"/>
+      <c r="C76" s="2"/>
     </row>
     <row r="77" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B77" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C77" s="2">
-        <v>4</v>
-      </c>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
     </row>
     <row r="78" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B78" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C78" s="2">
-        <v>4</v>
-      </c>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
     </row>
     <row r="79" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B79" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C79" s="2">
-        <v>4</v>
-      </c>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
     </row>
     <row r="80" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B80" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C80" s="2">
-        <v>4</v>
-      </c>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
     </row>
     <row r="81" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B81" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="C81" s="2">
-        <v>4</v>
-      </c>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
     </row>
     <row r="82" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B82" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C82" s="2">
-        <v>4</v>
-      </c>
+      <c r="B82" s="2"/>
+      <c r="C82" s="2"/>
     </row>
     <row r="83" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B83" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C83" s="2">
-        <v>4</v>
-      </c>
+      <c r="B83" s="2"/>
+      <c r="C83" s="2"/>
     </row>
     <row r="84" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B84" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C84" s="2">
-        <v>4</v>
-      </c>
+      <c r="B84" s="2"/>
+      <c r="C84" s="2"/>
     </row>
     <row r="85" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B85" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C85" s="2">
-        <v>4</v>
-      </c>
+      <c r="B85" s="2"/>
+      <c r="C85" s="2"/>
     </row>
     <row r="86" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B86" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C86" s="2">
-        <v>3</v>
-      </c>
+      <c r="B86" s="2"/>
+      <c r="C86" s="2"/>
     </row>
     <row r="87" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B87" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C87" s="2">
-        <v>3</v>
-      </c>
+      <c r="B87" s="2"/>
+      <c r="C87" s="2"/>
     </row>
     <row r="88" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B88" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C88" s="2">
-        <v>3</v>
-      </c>
+      <c r="B88" s="2"/>
+      <c r="C88" s="2"/>
     </row>
     <row r="89" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B89" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C89" s="2">
-        <v>2</v>
-      </c>
+      <c r="B89" s="2"/>
+      <c r="C89" s="2"/>
     </row>
     <row r="90" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B90" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C90" s="2">
-        <v>2</v>
-      </c>
+      <c r="B90" s="2"/>
+      <c r="C90" s="2"/>
     </row>
     <row r="91" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B91" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C91" s="2">
-        <v>2</v>
-      </c>
+      <c r="B91" s="2"/>
+      <c r="C91" s="2"/>
     </row>
     <row r="92" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B92" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C92" s="2">
-        <v>2</v>
-      </c>
+      <c r="B92" s="2"/>
+      <c r="C92" s="2"/>
     </row>
     <row r="93" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B93" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C93" s="2">
-        <v>2</v>
-      </c>
+      <c r="B93" s="2"/>
+      <c r="C93" s="2"/>
     </row>
     <row r="94" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B94" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C94" s="2">
-        <v>2</v>
-      </c>
+      <c r="B94" s="2"/>
+      <c r="C94" s="2"/>
     </row>
     <row r="95" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B95" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C95" s="2">
-        <v>2</v>
-      </c>
+      <c r="B95" s="2"/>
+      <c r="C95" s="2"/>
     </row>
     <row r="96" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B96" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C96" s="2">
-        <v>2</v>
-      </c>
+      <c r="B96" s="2"/>
+      <c r="C96" s="2"/>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B97" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C97" s="2">
-        <v>2</v>
-      </c>
+      <c r="B97" s="2"/>
+      <c r="C97" s="2"/>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B98" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C98" s="2">
-        <v>1</v>
-      </c>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B99" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C99" s="2">
-        <v>1</v>
-      </c>
+      <c r="B99" s="2"/>
+      <c r="C99" s="2"/>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B100" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C100" s="2">
-        <v>1</v>
-      </c>
+      <c r="B100" s="2"/>
+      <c r="C100" s="2"/>
     </row>
     <row r="101" spans="2:3" x14ac:dyDescent="0.6">
-      <c r="B101" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C101" s="2">
-        <v>1</v>
-      </c>
+      <c r="B101" s="2"/>
+      <c r="C101" s="2"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F1:F89">

--- a/knto_images(현황).xlsx
+++ b/knto_images(현황).xlsx
@@ -8,13 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\WebImages_travel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BBE3748-BFE5-4142-B6BA-F8911426B1FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E3F4F4-8B85-4D5B-BF76-8649A6CF4478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3983" yWindow="0" windowWidth="17865" windowHeight="12780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5895" yWindow="2115" windowWidth="14317" windowHeight="9217" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="전체" sheetId="1" r:id="rId1"/>
     <sheet name="서울" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="413">
   <si>
     <t>여행지명</t>
   </si>
@@ -322,9 +324,6 @@
     <t>국립현대미술관</t>
   </si>
   <si>
-    <t xml:space="preserve">경희궁: 3월 경희궁 봄 산책 가이드 (꽃 피는 길목 추천, 역사 스토리, 입장료 팁)  </t>
-  </si>
-  <si>
     <t>경희궁: 경희궁에서 만나는 3월의 고즈넉한 매력 (봄 행사 일정, 주변 카페 추천, 사진 촬영 포인트)</t>
   </si>
   <si>
@@ -337,43 +336,19 @@
     <t>경복궁: 경복궁 3월 특별 행사와 방문 팁 (수문장 교대식 일정, 주변 산책로, 주차 정보)</t>
   </si>
   <si>
-    <t xml:space="preserve">익선동 한옥거리: 3월 익선동 한옥거리 카페 탐방 (봄 분위기 카페 추천, 한옥 골목 산책 코스, 음식 메뉴 팁)  </t>
-  </si>
-  <si>
     <t>익선동 한옥거리: 익선동에서 느끼는 3월의 레트로 감성 (사진 명소, 주변 상점 가이드, 방문 시간 추천)</t>
   </si>
   <si>
     <t>서울남산: 서울남산 3월 야경과 데이트 스팟 (N서울타워 이벤트, 주변 레스토랑 추천, 교통 팁)</t>
   </si>
   <si>
-    <t xml:space="preserve">창덕궁: 3월 창덕궁 비밀의 정원 봄 탐험 (후원 입장 예약 팁, 꽃 피는 정원 가이드, 역사 이야기)  </t>
-  </si>
-  <si>
-    <t>창덕궁: 창덕궁에서 즐기는 3월 궁궐 피크닉 (봄 행사 일정, 주변 편의시설, 사진 촬영 팁)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">덕수궁: 3월 덕수궁 석조전과 봄 산책 (야간 개장 정보, 역사 전시 추천, 입장 팁)  </t>
-  </si>
-  <si>
     <t>덕수궁: 덕수궁 3월 문화 행사와 주변 투어 (콘서트 일정, 카페 추천, 교통 가이드)</t>
   </si>
   <si>
     <t>광화문: 광화문에서 만나는 3월 서울의 심장 (역사 산책 코스, 푸드트럭 팁, 방문 시간 추천)</t>
   </si>
   <si>
-    <t xml:space="preserve">창경궁: 3월 창경궁 온실과 봄꽃 만개 (온실 투어 가이드, 궁궐 이벤트, 입장료 정보)  </t>
-  </si>
-  <si>
-    <t>창경궁: 창경궁 3월 야간 관람 팁과 매력 (조명 행사 일정, 주변 산책로, 사진 촬영 스팟)</t>
-  </si>
-  <si>
     <t>수문장 교대의식: 수문장 교대의식과 함께하는 3월 궁궐 데이트 (의상 설명, 사진 팁, 입장 정보)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">국립현대미술관: 3월 국립현대미술관 봄 전시 추천 (특별전 일정, 관람 팁, 카페 휴식)  </t>
-  </si>
-  <si>
-    <t>국립현대미술관: 국립현대미술관에서 즐기는 3월 문화 데이 (작품 해설, 주변 산책 코스, 티켓 예매 가이드)</t>
   </si>
   <si>
     <t xml:space="preserve">광화문: 3월 광화문 광장 봄 축제 즐기기 (이벤트 스케줄, 주변 명소 연계, 사진 포인트)  </t>
@@ -534,12 +509,933 @@
     <t>들꽃수목원</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t xml:space="preserve">덕수궁: 3월 덕수궁 석조전과 봄 산책 (야간 개장 정보, 역사 전시 추천, 입장 팁)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">경희궁: 3월 경희궁 봄 산책 가이드 (꽃 피는 길목 추천, 역사 스토리, 입장료 팁)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">익선동 한옥거리: 3월 익선동 한옥거리 카페 탐방 (봄 분위기 카페 추천, 한옥 골목 산책 코스, 음식 메뉴 팁)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">국립현대미술관: 3월 국립현대미술관 봄 전시 추천 (특별전 일정, 관람 팁, 카페 휴식)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>🌸 뚝섬 전망문화콤플렉스</t>
+  </si>
+  <si>
+    <t>🌸 롯데월드타워</t>
+  </si>
+  <si>
+    <t>🌸 코엑스</t>
+  </si>
+  <si>
+    <t>1. 3월 서울 봄 산책 코스 – 뚝섬 전망문화콤플렉스에서 즐기는 한강 뷰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 봄날 한강 전망 명소, 뚝섬 전망문화콤플렉스 가볼만한 이유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 서울 봄나들이 추천 – 뚝섬 전망문화콤플렉스에서 만나는 한강 풍경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 3월 서울 데이트 코스 – 롯데월드타워 전망대에서 보는 봄 풍경</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 봄에 가면 더 좋은 롯데월드타워 여행 가이드 (전망대·맛집·포토존)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 서울 3월 실내 여행 추천 – 롯데월드타워 하루 코스 완벽 정리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">창덕궁: 3월 창덕궁 비밀의 정원 봄 탐험 (후원 입장 예약 팁, 꽃 피는 정원 가이드, 역사 이야기)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>엔카</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>플래폼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>등급</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>캘리그래피</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주행거리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사고유무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색상(외부)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>색(실내)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특이사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>베이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가격</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>렌트/ 기어봉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>무</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연식</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22/04</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>케이카</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>원주</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22/03</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>렌트/엔진부품 교환</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공영주차장 주소록 (총 125개)</t>
+  </si>
+  <si>
+    <t>일련번호</t>
+  </si>
+  <si>
+    <t>이름</t>
+  </si>
+  <si>
+    <t>주소</t>
+  </si>
+  <si>
+    <t>개화산역</t>
+  </si>
+  <si>
+    <t>강서구 방화동 845</t>
+  </si>
+  <si>
+    <t>개화역</t>
+  </si>
+  <si>
+    <t>강서구 개화동로8길 17</t>
+  </si>
+  <si>
+    <t>구로디지털단지역</t>
+  </si>
+  <si>
+    <t>구로구 도림천로 477</t>
+  </si>
+  <si>
+    <t>구파발역</t>
+  </si>
+  <si>
+    <t>은평구 진관동 66-30</t>
+  </si>
+  <si>
+    <t>가양라이폼</t>
+  </si>
+  <si>
+    <t>강서구 가양동 1457-1</t>
+  </si>
+  <si>
+    <t>도봉산역</t>
+  </si>
+  <si>
+    <t>도봉구 도봉동 288-19</t>
+  </si>
+  <si>
+    <t>동구로</t>
+  </si>
+  <si>
+    <t>구로구 가마산로 26길 27</t>
+  </si>
+  <si>
+    <t>동대문</t>
+  </si>
+  <si>
+    <t>중구 신당동 251-7</t>
+  </si>
+  <si>
+    <t>복정역</t>
+  </si>
+  <si>
+    <t>송파구 장지동 600-2</t>
+  </si>
+  <si>
+    <t>사당노외</t>
+  </si>
+  <si>
+    <t>서초구 방배동 507-1</t>
+  </si>
+  <si>
+    <t>서울글로벌센터</t>
+  </si>
+  <si>
+    <t>종로구 서린동 63</t>
+  </si>
+  <si>
+    <t>세종로</t>
+  </si>
+  <si>
+    <t>종로구 세종로 80-1(지하)</t>
+  </si>
+  <si>
+    <t>수서역</t>
+  </si>
+  <si>
+    <t>강남구 수서동 735(북)</t>
+  </si>
+  <si>
+    <t>신대방역</t>
+  </si>
+  <si>
+    <t>관악구 신림동 498</t>
+  </si>
+  <si>
+    <t>신방화역</t>
+  </si>
+  <si>
+    <t>강서구 마곡동 739</t>
+  </si>
+  <si>
+    <t>신설동</t>
+  </si>
+  <si>
+    <t>동대문구 신설동 114-29</t>
+  </si>
+  <si>
+    <t>신월4동</t>
+  </si>
+  <si>
+    <t>양천구 신월동 411-1(국회대로 28)</t>
+  </si>
+  <si>
+    <t>신천유수지</t>
+  </si>
+  <si>
+    <t>송파구 신천동 14(송파구 오금로1)</t>
+  </si>
+  <si>
+    <t>별우물</t>
+  </si>
+  <si>
+    <t>강동구 암사1동 473-3(고덕로24길 50)</t>
+  </si>
+  <si>
+    <t>영등포구청역</t>
+  </si>
+  <si>
+    <t>영등포구 당산동3가 370-3</t>
+  </si>
+  <si>
+    <t>용산주차빌딩</t>
+  </si>
+  <si>
+    <t>용산구 한강로2가 12-9</t>
+  </si>
+  <si>
+    <t>웃우물</t>
+  </si>
+  <si>
+    <t>양천구 신정동 943-25</t>
+  </si>
+  <si>
+    <t>일원터널</t>
+  </si>
+  <si>
+    <t>강남구 일원동 722-2</t>
+  </si>
+  <si>
+    <t>잠실역</t>
+  </si>
+  <si>
+    <t>송파구 신천동 27(지하)</t>
+  </si>
+  <si>
+    <t>장안1동</t>
+  </si>
+  <si>
+    <t>동대문구 답십리로66길 75(장안동)</t>
+  </si>
+  <si>
+    <t>장안2동</t>
+  </si>
+  <si>
+    <t>동대문구 장안동 286-9</t>
+  </si>
+  <si>
+    <t>종묘</t>
+  </si>
+  <si>
+    <t>종로구 훈정동 2</t>
+  </si>
+  <si>
+    <t>중곡1동</t>
+  </si>
+  <si>
+    <t>광진구 중곡1동 230-12(면목로 126)</t>
+  </si>
+  <si>
+    <t>천왕역</t>
+  </si>
+  <si>
+    <t>구로구 천왕동 14-38(오리로1156)</t>
+  </si>
+  <si>
+    <t>천호역</t>
+  </si>
+  <si>
+    <t>강동구 천호동 455(천호대로 997)</t>
+  </si>
+  <si>
+    <t>학여울역</t>
+  </si>
+  <si>
+    <t>강남구 대치동 514(남부순환로 3104)</t>
+  </si>
+  <si>
+    <t>한강진역</t>
+  </si>
+  <si>
+    <t>용산구 한남동 산10-84(728-27)</t>
+  </si>
+  <si>
+    <t>훈련원공원</t>
+  </si>
+  <si>
+    <t>중구 을지로5가 40-3(국립중앙의료원 옆)</t>
+  </si>
+  <si>
+    <t>DDP동측(양쪽)</t>
+  </si>
+  <si>
+    <t>중구 을지로(마장로22)</t>
+  </si>
+  <si>
+    <t>남대문 시장</t>
+  </si>
+  <si>
+    <t>중구 남창동 51-4 일대 (남대문 및 롯데손해보험 빌딩 앞)</t>
+  </si>
+  <si>
+    <t>남대문 초입</t>
+  </si>
+  <si>
+    <t>남산공원 소월로</t>
+  </si>
+  <si>
+    <t>용산구 소월길(백범광장맞은편) (중구 남대문로5가 450일대)</t>
+  </si>
+  <si>
+    <t>남산공원 소파로</t>
+  </si>
+  <si>
+    <t>중구 남창동 205-107 일대</t>
+  </si>
+  <si>
+    <t>남산예장</t>
+  </si>
+  <si>
+    <t>중구 퇴계로26길 36</t>
+  </si>
+  <si>
+    <t>동순라길(종묘)</t>
+  </si>
+  <si>
+    <t>종로구 인의동 112-10 일대</t>
+  </si>
+  <si>
+    <t>소파로케이블카앞</t>
+  </si>
+  <si>
+    <t>중구 회현동1가 산1-15</t>
+  </si>
+  <si>
+    <t>장충단로(한남광장)</t>
+  </si>
+  <si>
+    <t>용산구 한남동 산9-19</t>
+  </si>
+  <si>
+    <t>탑골공원</t>
+  </si>
+  <si>
+    <t>종로구 종로2가 38-4(대학로5길 97)</t>
+  </si>
+  <si>
+    <t>진흥로</t>
+  </si>
+  <si>
+    <t>은평구 역촌동 41-8</t>
+  </si>
+  <si>
+    <t>가양3동</t>
+  </si>
+  <si>
+    <t>강서구 가양동 1488-12</t>
+  </si>
+  <si>
+    <t>목동체비지</t>
+  </si>
+  <si>
+    <t>양천구 목동 908-26</t>
+  </si>
+  <si>
+    <t>방화역(동)</t>
+  </si>
+  <si>
+    <t>강서구 방화동 830-4</t>
+  </si>
+  <si>
+    <t>방화역(서)</t>
+  </si>
+  <si>
+    <t>강서구 방화동 829-1</t>
+  </si>
+  <si>
+    <t>가양역</t>
+  </si>
+  <si>
+    <t>강서구 가양동 1480-10</t>
+  </si>
+  <si>
+    <t>대림역2</t>
+  </si>
+  <si>
+    <t>구로구 구로동 73-9</t>
+  </si>
+  <si>
+    <t>가마산고가밑</t>
+  </si>
+  <si>
+    <t>구로구 구로동 414-13</t>
+  </si>
+  <si>
+    <t>가산동 금천교</t>
+  </si>
+  <si>
+    <t>금천구 가산동 677</t>
+  </si>
+  <si>
+    <t>구로디지털단지역(상)</t>
+  </si>
+  <si>
+    <t>관악구 신림동 1677-4</t>
+  </si>
+  <si>
+    <t>독산동 금천교</t>
+  </si>
+  <si>
+    <t>금천구 독산동 1081-4</t>
+  </si>
+  <si>
+    <t>온수역(남)</t>
+  </si>
+  <si>
+    <t>구로구 온수동 51-26</t>
+  </si>
+  <si>
+    <t>당산고가밑</t>
+  </si>
+  <si>
+    <t>영등포구 당산동5가 9-15</t>
+  </si>
+  <si>
+    <t>당산노외</t>
+  </si>
+  <si>
+    <t>영등포구 당산동3가 2-1</t>
+  </si>
+  <si>
+    <t>대림노외</t>
+  </si>
+  <si>
+    <t>구로구 구로동 120-3 외 8필지</t>
+  </si>
+  <si>
+    <t>대림역</t>
+  </si>
+  <si>
+    <t>영등포구 대림동 808-24</t>
+  </si>
+  <si>
+    <t>문래1동</t>
+  </si>
+  <si>
+    <t>영등포구 문래동3가 54-12</t>
+  </si>
+  <si>
+    <t>양평동(동)</t>
+  </si>
+  <si>
+    <t>영등포구 양평동5가 44-1(양평교하부)</t>
+  </si>
+  <si>
+    <t>동작대교(위)</t>
+  </si>
+  <si>
+    <t>서초구 반포동 1333-1, 동작구 동작동 316-3</t>
+  </si>
+  <si>
+    <t>봉천복개3</t>
+  </si>
+  <si>
+    <t>관악구 신림동 1467-3 ~ 4, 1467-6</t>
+  </si>
+  <si>
+    <t>여의서로</t>
+  </si>
+  <si>
+    <t>영등포구 여의도동 8-1</t>
+  </si>
+  <si>
+    <t>원효대교 남단</t>
+  </si>
+  <si>
+    <t>영등포구 여의도동 5</t>
+  </si>
+  <si>
+    <t>해군본부앞</t>
+  </si>
+  <si>
+    <t>영등포구 신길동 812</t>
+  </si>
+  <si>
+    <t>보라매상업</t>
+  </si>
+  <si>
+    <t>동작구 신대방동 431-3</t>
+  </si>
+  <si>
+    <t>여의도공원</t>
+  </si>
+  <si>
+    <t>영등포구 여의도동 2-11</t>
+  </si>
+  <si>
+    <t>동호대교(남)</t>
+  </si>
+  <si>
+    <t>강남구 압구정동 435 (동호대교하부 올림픽대로 진입부)</t>
+  </si>
+  <si>
+    <t>명일파출소</t>
+  </si>
+  <si>
+    <t>강동구 명일동 47-9(명일파출소 뒤)</t>
+  </si>
+  <si>
+    <t>성내역(잠실나루역)</t>
+  </si>
+  <si>
+    <t>송파구 신천동 11-1 (잠실나루역 교차로부근)</t>
+  </si>
+  <si>
+    <t>압구정고가1</t>
+  </si>
+  <si>
+    <t>강남구 신사동 668(압구정고가하부)</t>
+  </si>
+  <si>
+    <t>압구정고가2</t>
+  </si>
+  <si>
+    <t>영동6교밑</t>
+  </si>
+  <si>
+    <t>강남구 대치동 512-1(극동교회앞)</t>
+  </si>
+  <si>
+    <t>옥수역</t>
+  </si>
+  <si>
+    <t>성동구 옥수동 401-1(옥수역7번출구 부근)</t>
+  </si>
+  <si>
+    <t>일원역</t>
+  </si>
+  <si>
+    <t>강남구 일원본동 716-2</t>
+  </si>
+  <si>
+    <t>남부여성발전센터</t>
+  </si>
+  <si>
+    <t>금천구 시흥동 산139-2</t>
+  </si>
+  <si>
+    <t>영남</t>
+  </si>
+  <si>
+    <t>영등포구 영등포동4가 123</t>
+  </si>
+  <si>
+    <t>남대문화물</t>
+  </si>
+  <si>
+    <t>중구 남대문로4가 24-1(남대문로 18)</t>
+  </si>
+  <si>
+    <t>소파길노상</t>
+  </si>
+  <si>
+    <t>중구 회현동1가 산 1-19(소파로)</t>
+  </si>
+  <si>
+    <t>남산파출소</t>
+  </si>
+  <si>
+    <t>중구 회현동1가 147-32</t>
+  </si>
+  <si>
+    <t>동작대교</t>
+  </si>
+  <si>
+    <t>용산구 용산동6가 69-11 (금강아산병원측 이촌지하차도 상부)</t>
+  </si>
+  <si>
+    <t>남산한옥마을</t>
+  </si>
+  <si>
+    <t>중구 필동2가 83-1</t>
+  </si>
+  <si>
+    <t>동국제강</t>
+  </si>
+  <si>
+    <t>중구 삼각동 111-1</t>
+  </si>
+  <si>
+    <t>청계1</t>
+  </si>
+  <si>
+    <t>종로구 관철동 13-14</t>
+  </si>
+  <si>
+    <t>청계2</t>
+  </si>
+  <si>
+    <t>종로구 관수동 91-4</t>
+  </si>
+  <si>
+    <t>청계3</t>
+  </si>
+  <si>
+    <t>종로구 예지동 140-1</t>
+  </si>
+  <si>
+    <t>청계5</t>
+  </si>
+  <si>
+    <t>종로구 종로5가 458-2</t>
+  </si>
+  <si>
+    <t>청계6</t>
+  </si>
+  <si>
+    <t>중구 신당동 217-118 종로구 창신동 436-91</t>
+  </si>
+  <si>
+    <t>청계6 (신평화시장앞)</t>
+  </si>
+  <si>
+    <t>종로구 창신동 436-91</t>
+  </si>
+  <si>
+    <t>청계7</t>
+  </si>
+  <si>
+    <t>종로구 창신동 436-87</t>
+  </si>
+  <si>
+    <t>돈화문로</t>
+  </si>
+  <si>
+    <t>중구 을지로3가 296-24(도로양쪽)</t>
+  </si>
+  <si>
+    <t>마른내길</t>
+  </si>
+  <si>
+    <t>중구 인현동1가 87-8</t>
+  </si>
+  <si>
+    <t>배오개길</t>
+  </si>
+  <si>
+    <t>중구 예관동 22-1</t>
+  </si>
+  <si>
+    <t>을지로</t>
+  </si>
+  <si>
+    <t>중구 을지로3가 282-8</t>
+  </si>
+  <si>
+    <t>청계8</t>
+  </si>
+  <si>
+    <t>동대문구 신설동 109-2</t>
+  </si>
+  <si>
+    <t>청계8가</t>
+  </si>
+  <si>
+    <t>중구 흥인동 162-1</t>
+  </si>
+  <si>
+    <t>당고개위</t>
+  </si>
+  <si>
+    <t>노원구 상계동 111-567(도로양쪽)</t>
+  </si>
+  <si>
+    <t>도봉로 15길</t>
+  </si>
+  <si>
+    <t>강북구 미아동 458-7</t>
+  </si>
+  <si>
+    <t>도봉산</t>
+  </si>
+  <si>
+    <t>도봉구 도봉동 282-26</t>
+  </si>
+  <si>
+    <t>석계역</t>
+  </si>
+  <si>
+    <t>노원구 월계동 50-9</t>
+  </si>
+  <si>
+    <t>창동역(서)</t>
+  </si>
+  <si>
+    <t>도봉구 창동 330</t>
+  </si>
+  <si>
+    <t>반포천</t>
+  </si>
+  <si>
+    <t>서초구 반포동 118-3</t>
+  </si>
+  <si>
+    <t>관철동</t>
+  </si>
+  <si>
+    <t>종로구 관철동 11-4, 11-14(보도블럭)</t>
+  </si>
+  <si>
+    <t>남산소파길식당</t>
+  </si>
+  <si>
+    <t>중구 예장동 8-189</t>
+  </si>
+  <si>
+    <t>마른내로</t>
+  </si>
+  <si>
+    <t>중구 오장동 69-3</t>
+  </si>
+  <si>
+    <t>청계5가</t>
+  </si>
+  <si>
+    <t>중구 을지로6가 17-442</t>
+  </si>
+  <si>
+    <t>공항동(송정역)</t>
+  </si>
+  <si>
+    <t>강서구 공항동 42-8</t>
+  </si>
+  <si>
+    <t>망원동</t>
+  </si>
+  <si>
+    <t>마포구 망원동 478-10</t>
+  </si>
+  <si>
+    <t>목동노외</t>
+  </si>
+  <si>
+    <t>양천구 목동 905-32</t>
+  </si>
+  <si>
+    <t>미근동</t>
+  </si>
+  <si>
+    <t>서대문구 미근동 267-3</t>
+  </si>
+  <si>
+    <t>방화우체국</t>
+  </si>
+  <si>
+    <t>강서구 방화동 824</t>
+  </si>
+  <si>
+    <t>성북초교</t>
+  </si>
+  <si>
+    <t>성북구 성북동 125</t>
+  </si>
+  <si>
+    <t>온수역(북)</t>
+  </si>
+  <si>
+    <t>구로구 온수동 20-10 일대</t>
+  </si>
+  <si>
+    <t>올림픽대교(북)</t>
+  </si>
+  <si>
+    <t>광진구 구의동 올림픽대교(하부)</t>
+  </si>
+  <si>
+    <t>월계역</t>
+  </si>
+  <si>
+    <t>노원구 월계동 320-2</t>
+  </si>
+  <si>
+    <t>일원동</t>
+  </si>
+  <si>
+    <t>강남구 일원동 711-2</t>
+  </si>
+  <si>
+    <t>종암1동</t>
+  </si>
+  <si>
+    <t>성북구 종암동 133-8</t>
+  </si>
+  <si>
+    <t>증가로</t>
+  </si>
+  <si>
+    <t>서대문구 북가좌동 359-5</t>
+  </si>
+  <si>
+    <t>면목유수지</t>
+  </si>
+  <si>
+    <t>중랑구 면목동 168-2</t>
+  </si>
+  <si>
+    <t>중랑동부시장</t>
+  </si>
+  <si>
+    <t>중랑구 면목2동 183-14</t>
+  </si>
+  <si>
+    <t>봉화산역(남)</t>
+  </si>
+  <si>
+    <t>중랑구 신내동 647</t>
+  </si>
+  <si>
+    <t>마장동</t>
+  </si>
+  <si>
+    <t>성동구 마장동 459-6</t>
+  </si>
+  <si>
+    <t>르블랑</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>22/11</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>천안</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창덕궁: 창덕궁에서 즐기는 3월 궁궐 피크닉 (봄 행사 일정, 주변 편의시설, 사진 촬영 팁)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 3월 서울 실내 데이트 – 코엑스에서 즐기는 봄 나들이 코스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 비 오는 봄날에도 좋은 서울 여행지, 코엑스 완벽 가이드</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 3월 가볼만한 서울 명소 – 코엑스 별마당도서관부터 쇼핑까지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">창경궁: 3월 창경궁 온실과 봄꽃 만개 (온실 투어 가이드, 궁궐 이벤트, 입장료 정보)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>창경궁: 창경궁 3월 야간 관람 팁과 매력 (조명 행사 일정, 주변 산책로, 사진 촬영 스팟)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -580,8 +1476,46 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -612,6 +1546,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -625,7 +1571,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -646,6 +1592,38 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -954,7 +1932,7 @@
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B3" s="9" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="C3" s="2">
         <v>10</v>
@@ -962,7 +1940,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B4" s="10" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="C4" s="2">
         <v>9</v>
@@ -970,7 +1948,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B5" s="9" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="C5" s="2">
         <v>8</v>
@@ -978,7 +1956,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B6" s="9" t="s">
-        <v>127</v>
+        <v>118</v>
       </c>
       <c r="C6" s="2">
         <v>8</v>
@@ -986,7 +1964,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B7" s="10" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="C7" s="2">
         <v>6</v>
@@ -1819,8 +2797,8 @@
       <c r="C2" s="5">
         <v>9</v>
       </c>
-      <c r="F2" t="s">
-        <v>97</v>
+      <c r="F2" s="12" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.6">
@@ -1834,7 +2812,7 @@
         <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.6">
@@ -1860,7 +2838,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.6">
@@ -1874,7 +2852,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.6">
@@ -1899,8 +2877,8 @@
       <c r="C8" s="5">
         <v>6</v>
       </c>
-      <c r="F8" t="s">
-        <v>100</v>
+      <c r="F8" s="12" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.6">
@@ -1914,7 +2892,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.6">
@@ -1939,8 +2917,8 @@
       <c r="C11" s="5">
         <v>2</v>
       </c>
-      <c r="F11" s="1" t="s">
-        <v>102</v>
+      <c r="F11" s="11" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.6">
@@ -1954,7 +2932,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.6">
@@ -1970,29 +2948,29 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A14" s="1" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.6">
       <c r="B15" s="1" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.6">
       <c r="B16" s="1" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="C16" s="1">
         <v>6</v>
@@ -2000,20 +2978,20 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B17" s="1" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="C17" s="1">
         <v>6</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>105</v>
+      <c r="F17" s="22" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="F18" s="1" t="s">
-        <v>106</v>
+      <c r="F18" s="22" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.6">
@@ -2023,15 +3001,15 @@
     <row r="20" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
-      <c r="F20" s="1" t="s">
-        <v>107</v>
+      <c r="F20" s="11" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="F21" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.6">
@@ -2042,14 +3020,14 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="F23" s="6" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="F24" s="1" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.6">
@@ -2059,15 +3037,15 @@
     <row r="26" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
-      <c r="F26" s="1" t="s">
-        <v>110</v>
+      <c r="F26" s="22" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
-      <c r="F27" s="1" t="s">
-        <v>111</v>
+      <c r="F27" s="22" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.6">
@@ -2078,14 +3056,14 @@
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="F29" s="7" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="F30" s="1" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.6">
@@ -2095,138 +3073,186 @@
     <row r="32" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
-      <c r="F32" s="1" t="s">
-        <v>113</v>
+      <c r="F32" s="11" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="F33" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.6">
+    </row>
+    <row r="34" spans="2:6" ht="27" x14ac:dyDescent="0.6">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
+      <c r="F34" s="13" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
+      <c r="F35" s="14"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
+      <c r="F36" s="15" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
+      <c r="F37" s="14"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
+      <c r="F38" s="15" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
+      <c r="F39" s="16"/>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
+      <c r="F40" s="15" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
+      <c r="F41"/>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
+      <c r="F42"/>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="F43"/>
+    </row>
+    <row r="44" spans="2:6" ht="27" x14ac:dyDescent="0.6">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
+      <c r="F44" s="13" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
+      <c r="F45" s="14"/>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
+      <c r="F46" s="15" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
+      <c r="F47" s="16"/>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
-    </row>
-    <row r="49" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F48" s="15" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
-    </row>
-    <row r="50" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F49" s="16"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
-    </row>
-    <row r="51" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F50" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
-    </row>
-    <row r="52" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F51"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
-    </row>
-    <row r="53" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F52"/>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
-    </row>
-    <row r="54" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F53"/>
+    </row>
+    <row r="54" spans="2:6" ht="27" x14ac:dyDescent="0.6">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
-    </row>
-    <row r="55" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F54" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-    </row>
-    <row r="56" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F55" s="14"/>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
-    </row>
-    <row r="57" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F56" s="23" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
-    </row>
-    <row r="58" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F57" s="24"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
-    </row>
-    <row r="59" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F58" s="23" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
-    </row>
-    <row r="60" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F59" s="24"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
-    </row>
-    <row r="61" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F60" s="23" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
     </row>
-    <row r="63" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="63" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
     </row>
-    <row r="64" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="64" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
     </row>
@@ -2386,4 +3412,1558 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF141B82-E770-459A-B61E-AA19C7A0D3EE}">
+  <dimension ref="A1:J6"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="2" max="2" width="12.5625" customWidth="1"/>
+    <col min="3" max="3" width="9.25" style="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.5625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="D1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F1" t="s">
+        <v>140</v>
+      </c>
+      <c r="G1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H1" t="s">
+        <v>145</v>
+      </c>
+      <c r="I1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="D2" s="17">
+        <v>107698</v>
+      </c>
+      <c r="E2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" t="s">
+        <v>143</v>
+      </c>
+      <c r="G2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H2" s="17">
+        <v>2830</v>
+      </c>
+      <c r="I2" t="s">
+        <v>146</v>
+      </c>
+      <c r="J2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A3" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" t="s">
+        <v>403</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>404</v>
+      </c>
+      <c r="D4" s="17">
+        <v>122676</v>
+      </c>
+      <c r="F4" t="s">
+        <v>405</v>
+      </c>
+      <c r="G4" t="s">
+        <v>405</v>
+      </c>
+      <c r="H4" s="17">
+        <v>2420</v>
+      </c>
+      <c r="J4" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A5" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.6">
+      <c r="A6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="17">
+        <v>107729</v>
+      </c>
+      <c r="E6" t="s">
+        <v>147</v>
+      </c>
+      <c r="F6" t="s">
+        <v>143</v>
+      </c>
+      <c r="G6" t="s">
+        <v>144</v>
+      </c>
+      <c r="H6" s="17">
+        <v>2930</v>
+      </c>
+      <c r="I6" t="s">
+        <v>154</v>
+      </c>
+      <c r="J6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5C2ECD-FC40-4B62-B0AC-B688596AF17A}">
+  <dimension ref="A1:C128"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="11.5625" customWidth="1"/>
+    <col min="2" max="2" width="20.25" customWidth="1"/>
+    <col min="3" max="3" width="27.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.6">
+      <c r="A1" s="19" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A3" s="20" t="s">
+        <v>156</v>
+      </c>
+      <c r="B3" s="20" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A4" s="21">
+        <v>1</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A5" s="21">
+        <v>2</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A6" s="21">
+        <v>3</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A7" s="21">
+        <v>4</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A8" s="21">
+        <v>5</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A9" s="21">
+        <v>6</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A10" s="21">
+        <v>7</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A11" s="21">
+        <v>8</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A12" s="21">
+        <v>9</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C12" s="21" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A13" s="21">
+        <v>10</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C13" s="21" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A14" s="21">
+        <v>11</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C14" s="21" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A15" s="21">
+        <v>12</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C15" s="21" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A16" s="21">
+        <v>13</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="21" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A17" s="21">
+        <v>14</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A18" s="21">
+        <v>15</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C18" s="21" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A19" s="21">
+        <v>16</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A20" s="21">
+        <v>17</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="C20" s="21" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A21" s="21">
+        <v>18</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C21" s="21" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A22" s="21">
+        <v>19</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A23" s="21">
+        <v>20</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="C23" s="21" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A24" s="21">
+        <v>21</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="C24" s="21" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A25" s="21">
+        <v>22</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C25" s="21" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A26" s="21">
+        <v>23</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="C26" s="21" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A27" s="21">
+        <v>24</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C27" s="21" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A28" s="21">
+        <v>25</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C28" s="21" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A29" s="21">
+        <v>26</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C29" s="21" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A30" s="21">
+        <v>27</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A31" s="21">
+        <v>28</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C31" s="21" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A32" s="21">
+        <v>29</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="C32" s="21" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A33" s="21">
+        <v>30</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C33" s="21" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A34" s="21">
+        <v>31</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C34" s="21" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A35" s="21">
+        <v>32</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="C35" s="21" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A36" s="21">
+        <v>33</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="C36" s="21" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A37" s="21">
+        <v>34</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="C37" s="21" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A38" s="21">
+        <v>35</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>227</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A39" s="21">
+        <v>36</v>
+      </c>
+      <c r="B39" s="21" t="s">
+        <v>229</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A40" s="21">
+        <v>37</v>
+      </c>
+      <c r="B40" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="21" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A41" s="21">
+        <v>38</v>
+      </c>
+      <c r="B41" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C41" s="21" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A42" s="21">
+        <v>39</v>
+      </c>
+      <c r="B42" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="C42" s="21" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A43" s="21">
+        <v>40</v>
+      </c>
+      <c r="B43" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="C43" s="21" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A44" s="21">
+        <v>41</v>
+      </c>
+      <c r="B44" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A45" s="21">
+        <v>42</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A46" s="21">
+        <v>43</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A47" s="21">
+        <v>44</v>
+      </c>
+      <c r="B47" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A48" s="21">
+        <v>45</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A49" s="21">
+        <v>46</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A50" s="21">
+        <v>47</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A51" s="21">
+        <v>48</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A52" s="21">
+        <v>49</v>
+      </c>
+      <c r="B52" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A53" s="21">
+        <v>50</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A54" s="21">
+        <v>51</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A55" s="21">
+        <v>52</v>
+      </c>
+      <c r="B55" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C55" s="21" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A56" s="21">
+        <v>53</v>
+      </c>
+      <c r="B56" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C56" s="21" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A57" s="21">
+        <v>54</v>
+      </c>
+      <c r="B57" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C57" s="21" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A58" s="21">
+        <v>55</v>
+      </c>
+      <c r="B58" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A59" s="21">
+        <v>56</v>
+      </c>
+      <c r="B59" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C59" s="21" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A60" s="21">
+        <v>57</v>
+      </c>
+      <c r="B60" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="C60" s="21" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A61" s="21">
+        <v>58</v>
+      </c>
+      <c r="B61" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="C61" s="21" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A62" s="21">
+        <v>59</v>
+      </c>
+      <c r="B62" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="C62" s="21" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A63" s="21">
+        <v>60</v>
+      </c>
+      <c r="B63" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C63" s="21" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A64" s="21">
+        <v>61</v>
+      </c>
+      <c r="B64" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="C64" s="21" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A65" s="21">
+        <v>62</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A66" s="21">
+        <v>63</v>
+      </c>
+      <c r="B66" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="C66" s="21" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A67" s="21">
+        <v>64</v>
+      </c>
+      <c r="B67" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="C67" s="21" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A68" s="21">
+        <v>65</v>
+      </c>
+      <c r="B68" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C68" s="21" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A69" s="21">
+        <v>66</v>
+      </c>
+      <c r="B69" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A70" s="21">
+        <v>67</v>
+      </c>
+      <c r="B70" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A71" s="21">
+        <v>68</v>
+      </c>
+      <c r="B71" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A72" s="21">
+        <v>69</v>
+      </c>
+      <c r="B72" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A73" s="21">
+        <v>70</v>
+      </c>
+      <c r="B73" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A74" s="21">
+        <v>71</v>
+      </c>
+      <c r="B74" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A75" s="21">
+        <v>72</v>
+      </c>
+      <c r="B75" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A76" s="21">
+        <v>73</v>
+      </c>
+      <c r="B76" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A77" s="21">
+        <v>74</v>
+      </c>
+      <c r="B77" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A78" s="21">
+        <v>75</v>
+      </c>
+      <c r="B78" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A79" s="21">
+        <v>76</v>
+      </c>
+      <c r="B79" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A80" s="21">
+        <v>77</v>
+      </c>
+      <c r="B80" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="C80" s="21" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A81" s="21">
+        <v>78</v>
+      </c>
+      <c r="B81" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A82" s="21">
+        <v>79</v>
+      </c>
+      <c r="B82" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C82" s="21" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A83" s="21">
+        <v>80</v>
+      </c>
+      <c r="B83" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="C83" s="21" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A84" s="21">
+        <v>81</v>
+      </c>
+      <c r="B84" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="C84" s="21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A85" s="21">
+        <v>82</v>
+      </c>
+      <c r="B85" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="C85" s="21" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A86" s="21">
+        <v>83</v>
+      </c>
+      <c r="B86" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="C86" s="21" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A87" s="21">
+        <v>84</v>
+      </c>
+      <c r="B87" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C87" s="21" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A88" s="21">
+        <v>85</v>
+      </c>
+      <c r="B88" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C88" s="21" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A89" s="21">
+        <v>86</v>
+      </c>
+      <c r="B89" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C89" s="21" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A90" s="21">
+        <v>87</v>
+      </c>
+      <c r="B90" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C90" s="21" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A91" s="21">
+        <v>88</v>
+      </c>
+      <c r="B91" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="C91" s="21" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A92" s="21">
+        <v>89</v>
+      </c>
+      <c r="B92" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C92" s="21" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A93" s="21">
+        <v>90</v>
+      </c>
+      <c r="B93" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C93" s="21" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A94" s="21">
+        <v>91</v>
+      </c>
+      <c r="B94" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C94" s="21" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A95" s="21">
+        <v>92</v>
+      </c>
+      <c r="B95" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="C95" s="21" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A96" s="21">
+        <v>93</v>
+      </c>
+      <c r="B96" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C96" s="21" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A97" s="21">
+        <v>94</v>
+      </c>
+      <c r="B97" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="C97" s="21" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A98" s="21">
+        <v>95</v>
+      </c>
+      <c r="B98" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="C98" s="21" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A99" s="21">
+        <v>96</v>
+      </c>
+      <c r="B99" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="C99" s="21" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A100" s="21">
+        <v>97</v>
+      </c>
+      <c r="B100" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="C100" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A101" s="21">
+        <v>98</v>
+      </c>
+      <c r="B101" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="C101" s="21" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A102" s="21">
+        <v>99</v>
+      </c>
+      <c r="B102" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="C102" s="21" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A103" s="21">
+        <v>100</v>
+      </c>
+      <c r="B103" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="C103" s="21" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A104" s="21">
+        <v>101</v>
+      </c>
+      <c r="B104" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C104" s="21" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A105" s="21">
+        <v>102</v>
+      </c>
+      <c r="B105" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="C105" s="21" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A106" s="21">
+        <v>103</v>
+      </c>
+      <c r="B106" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="C106" s="21" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A107" s="21">
+        <v>104</v>
+      </c>
+      <c r="B107" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C107" s="21" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A108" s="21">
+        <v>105</v>
+      </c>
+      <c r="B108" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="C108" s="21" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+      <c r="A109" s="21">
+        <v>106</v>
+      </c>
+      <c r="B109" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="C109" s="21" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A110" s="21">
+        <v>107</v>
+      </c>
+      <c r="B110" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="C110" s="21" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A111" s="21">
+        <v>108</v>
+      </c>
+      <c r="B111" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="C111" s="21" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A112" s="21">
+        <v>109</v>
+      </c>
+      <c r="B112" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="C112" s="21" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A113" s="21">
+        <v>110</v>
+      </c>
+      <c r="B113" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="C113" s="21" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A114" s="21">
+        <v>111</v>
+      </c>
+      <c r="B114" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="C114" s="21" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A115" s="21">
+        <v>112</v>
+      </c>
+      <c r="B115" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="C115" s="21" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A116" s="21">
+        <v>113</v>
+      </c>
+      <c r="B116" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="C116" s="21" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A117" s="21">
+        <v>114</v>
+      </c>
+      <c r="B117" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="C117" s="21" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A118" s="21">
+        <v>115</v>
+      </c>
+      <c r="B118" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="C118" s="21" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A119" s="21">
+        <v>116</v>
+      </c>
+      <c r="B119" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="C119" s="21" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A120" s="21">
+        <v>117</v>
+      </c>
+      <c r="B120" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C120" s="21" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A121" s="21">
+        <v>118</v>
+      </c>
+      <c r="B121" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="C121" s="21" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A122" s="21">
+        <v>119</v>
+      </c>
+      <c r="B122" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="C122" s="21" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A123" s="21">
+        <v>120</v>
+      </c>
+      <c r="B123" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C123" s="21" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A124" s="21">
+        <v>121</v>
+      </c>
+      <c r="B124" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="C124" s="21" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A125" s="21">
+        <v>122</v>
+      </c>
+      <c r="B125" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="C125" s="21" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A126" s="21">
+        <v>123</v>
+      </c>
+      <c r="B126" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="C126" s="21" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A127" s="21">
+        <v>124</v>
+      </c>
+      <c r="B127" s="21" t="s">
+        <v>399</v>
+      </c>
+      <c r="C127" s="21" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.6">
+      <c r="A128" s="21">
+        <v>125</v>
+      </c>
+      <c r="B128" s="21" t="s">
+        <v>401</v>
+      </c>
+      <c r="C128" s="21" t="s">
+        <v>402</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/knto_images(현황).xlsx
+++ b/knto_images(현황).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\WebImages_travel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E3F4F4-8B85-4D5B-BF76-8649A6CF4478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BA8804-6326-4C55-B793-BB4E1B6177E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5895" yWindow="2115" windowWidth="14317" windowHeight="9217" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6128" yWindow="60" windowWidth="14309" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="전체" sheetId="1" r:id="rId1"/>
@@ -324,9 +324,6 @@
     <t>국립현대미술관</t>
   </si>
   <si>
-    <t>경희궁: 경희궁에서 만나는 3월의 고즈넉한 매력 (봄 행사 일정, 주변 카페 추천, 사진 촬영 포인트)</t>
-  </si>
-  <si>
     <t xml:space="preserve">명동거리: 3월 명동거리 쇼핑 &amp; 먹거리 투어 (봄 세일 정보, 스트리트 푸드 베스트, 교통 팁)  </t>
   </si>
   <si>
@@ -345,14 +342,7 @@
     <t>덕수궁: 덕수궁 3월 문화 행사와 주변 투어 (콘서트 일정, 카페 추천, 교통 가이드)</t>
   </si>
   <si>
-    <t>광화문: 광화문에서 만나는 3월 서울의 심장 (역사 산책 코스, 푸드트럭 팁, 방문 시간 추천)</t>
-  </si>
-  <si>
     <t>수문장 교대의식: 수문장 교대의식과 함께하는 3월 궁궐 데이트 (의상 설명, 사진 팁, 입장 정보)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">광화문: 3월 광화문 광장 봄 축제 즐기기 (이벤트 스케줄, 주변 명소 연계, 사진 포인트)  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve">수문장 교대의식: 3월 수문장 교대의식 관람 가이드 (공연 시간표, 베스트 뷰 포인트, 주변 궁궐 연계)  </t>
@@ -1428,6 +1418,18 @@
   </si>
   <si>
     <t>창경궁: 창경궁 3월 야간 관람 팁과 매력 (조명 행사 일정, 주변 산책로, 사진 촬영 스팟)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광화문: 광화문에서 만나는 3월 서울의 심장 (역사 산책 코스, 푸드트럭 팁, 방문 시간 추천)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">광화문: 4월 광화문 광장 봄 축제 즐기기 (이벤트 스케줄, 주변 명소 연계, 사진 포인트)  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>경희궁: 경희궁에서 만나는 4월의 고즈넉한 매력 (봄 행사 일정, 주변 카페 추천, 사진 촬영 포인트)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1571,7 +1573,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1625,6 +1627,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1932,7 +1935,7 @@
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B3" s="9" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C3" s="2">
         <v>10</v>
@@ -1940,7 +1943,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B4" s="10" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C4" s="2">
         <v>9</v>
@@ -1948,7 +1951,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B5" s="9" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C5" s="2">
         <v>8</v>
@@ -1956,7 +1959,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B6" s="9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C6" s="2">
         <v>8</v>
@@ -1964,7 +1967,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B7" s="10" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C7" s="2">
         <v>6</v>
@@ -2798,7 +2801,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.6">
@@ -2811,8 +2814,8 @@
       <c r="C3" s="5">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
-        <v>97</v>
+      <c r="F3" s="25" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.6">
@@ -2838,7 +2841,7 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.6">
@@ -2852,7 +2855,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.6">
@@ -2878,7 +2881,7 @@
         <v>6</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.6">
@@ -2892,7 +2895,7 @@
         <v>5</v>
       </c>
       <c r="F9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.6">
@@ -2918,7 +2921,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.6">
@@ -2932,7 +2935,7 @@
         <v>1</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.6">
@@ -2948,29 +2951,29 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A14" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.6">
       <c r="B15" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.6">
       <c r="B16" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C16" s="1">
         <v>6</v>
@@ -2978,20 +2981,20 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B17" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="F18" s="22" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.6">
@@ -3002,14 +3005,14 @@
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
       <c r="F20" s="11" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="F21" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.6">
@@ -3020,14 +3023,14 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="F23" s="6" t="s">
-        <v>106</v>
+        <v>411</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
-      <c r="F24" s="1" t="s">
-        <v>104</v>
+      <c r="F24" s="4" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.6">
@@ -3038,14 +3041,14 @@
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="F26" s="22" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="F27" s="22" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.6">
@@ -3056,14 +3059,14 @@
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="F29" s="7" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="F30" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.6">
@@ -3074,7 +3077,7 @@
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="F32" s="11" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.6">
@@ -3085,7 +3088,7 @@
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="F34" s="13" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.6">
@@ -3097,7 +3100,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="F36" s="15" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.6">
@@ -3109,7 +3112,7 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="F38" s="15" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.6">
@@ -3121,7 +3124,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="F40" s="15" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.6">
@@ -3143,7 +3146,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="F44" s="13" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.6">
@@ -3155,7 +3158,7 @@
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="F46" s="15" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.6">
@@ -3167,7 +3170,7 @@
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="F48" s="15" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.6">
@@ -3179,7 +3182,7 @@
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="F50" s="15" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.6">
@@ -3201,7 +3204,7 @@
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="F54" s="13" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.6">
@@ -3213,7 +3216,7 @@
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="F56" s="23" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.6">
@@ -3225,7 +3228,7 @@
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="F58" s="23" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.6">
@@ -3237,7 +3240,7 @@
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="F60" s="23" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.6">
@@ -3426,131 +3429,131 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
+        <v>132</v>
+      </c>
+      <c r="B1" t="s">
+        <v>133</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D1" t="s">
         <v>135</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
         <v>136</v>
       </c>
-      <c r="C1" s="18" t="s">
-        <v>148</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" t="s">
         <v>138</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
+        <v>142</v>
+      </c>
+      <c r="I1" t="s">
         <v>139</v>
-      </c>
-      <c r="F1" t="s">
-        <v>140</v>
-      </c>
-      <c r="G1" t="s">
-        <v>141</v>
-      </c>
-      <c r="H1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I1" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" t="s">
         <v>134</v>
       </c>
-      <c r="B2" t="s">
-        <v>137</v>
-      </c>
       <c r="C2" s="18" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D2" s="17">
         <v>107698</v>
       </c>
       <c r="E2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H2" s="17">
         <v>2830</v>
       </c>
       <c r="I2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B4" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D4" s="17">
         <v>122676</v>
       </c>
       <c r="F4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="G4" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="H4" s="17">
         <v>2420</v>
       </c>
       <c r="J4" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="18" t="s">
         <v>150</v>
-      </c>
-      <c r="B6" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>153</v>
       </c>
       <c r="D6" s="17">
         <v>107729</v>
       </c>
       <c r="E6" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F6" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="G6" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="H6" s="17">
         <v>2930</v>
       </c>
       <c r="I6" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J6" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -3572,18 +3575,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.6">
       <c r="A1" s="19" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" s="20" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C3" s="20" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.6">
@@ -3591,10 +3594,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C4" s="21" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.6">
@@ -3602,10 +3605,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.6">
@@ -3613,10 +3616,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C6" s="21" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.6">
@@ -3624,10 +3627,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.6">
@@ -3635,10 +3638,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="21" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C8" s="21" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.6">
@@ -3646,10 +3649,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.6">
@@ -3657,10 +3660,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="21" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C10" s="21" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.6">
@@ -3668,10 +3671,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.6">
@@ -3679,10 +3682,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.6">
@@ -3690,10 +3693,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="21" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.6">
@@ -3701,10 +3704,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="21" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C14" s="21" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.6">
@@ -3712,10 +3715,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.6">
@@ -3723,10 +3726,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.6">
@@ -3734,10 +3737,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="21" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.6">
@@ -3745,10 +3748,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C18" s="21" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.6">
@@ -3756,10 +3759,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3767,10 +3770,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3778,10 +3781,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3789,10 +3792,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="21" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="C22" s="21" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.6">
@@ -3800,10 +3803,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="21" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C23" s="21" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.6">
@@ -3811,10 +3814,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="21" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.6">
@@ -3822,10 +3825,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.6">
@@ -3833,10 +3836,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="21" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.6">
@@ -3844,10 +3847,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="21" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3855,10 +3858,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="21" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.6">
@@ -3866,10 +3869,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.6">
@@ -3877,10 +3880,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3888,10 +3891,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="21" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3899,10 +3902,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="21" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3910,10 +3913,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="21" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3921,10 +3924,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="21" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.6">
@@ -3932,10 +3935,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="21" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3943,10 +3946,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="21" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.6">
@@ -3954,10 +3957,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="21" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3965,10 +3968,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3976,10 +3979,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3987,10 +3990,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.6">
@@ -3998,10 +4001,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.6">
@@ -4009,10 +4012,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.6">
@@ -4020,10 +4023,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.6">
@@ -4031,10 +4034,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.6">
@@ -4042,10 +4045,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4053,10 +4056,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.6">
@@ -4064,10 +4067,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="21" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C47" s="21" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.6">
@@ -4075,10 +4078,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.6">
@@ -4086,10 +4089,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.6">
@@ -4097,10 +4100,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="21" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.6">
@@ -4108,10 +4111,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.6">
@@ -4119,10 +4122,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.6">
@@ -4130,10 +4133,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="21" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C53" s="21" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.6">
@@ -4141,10 +4144,10 @@
         <v>51</v>
       </c>
       <c r="B54" s="21" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C54" s="21" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.6">
@@ -4152,10 +4155,10 @@
         <v>52</v>
       </c>
       <c r="B55" s="21" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C55" s="21" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.6">
@@ -4163,10 +4166,10 @@
         <v>53</v>
       </c>
       <c r="B56" s="21" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C56" s="21" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.6">
@@ -4174,10 +4177,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="21" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C57" s="21" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.6">
@@ -4185,10 +4188,10 @@
         <v>55</v>
       </c>
       <c r="B58" s="21" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C58" s="21" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.6">
@@ -4196,10 +4199,10 @@
         <v>56</v>
       </c>
       <c r="B59" s="21" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C59" s="21" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.6">
@@ -4207,10 +4210,10 @@
         <v>57</v>
       </c>
       <c r="B60" s="21" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C60" s="21" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.6">
@@ -4218,10 +4221,10 @@
         <v>58</v>
       </c>
       <c r="B61" s="21" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C61" s="21" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.6">
@@ -4229,10 +4232,10 @@
         <v>59</v>
       </c>
       <c r="B62" s="21" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C62" s="21" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.6">
@@ -4240,10 +4243,10 @@
         <v>60</v>
       </c>
       <c r="B63" s="21" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C63" s="21" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4251,10 +4254,10 @@
         <v>61</v>
       </c>
       <c r="B64" s="21" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C64" s="21" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4262,10 +4265,10 @@
         <v>62</v>
       </c>
       <c r="B65" s="21" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C65" s="21" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4273,10 +4276,10 @@
         <v>63</v>
       </c>
       <c r="B66" s="21" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C66" s="21" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.6">
@@ -4284,10 +4287,10 @@
         <v>64</v>
       </c>
       <c r="B67" s="21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C67" s="21" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.6">
@@ -4295,10 +4298,10 @@
         <v>65</v>
       </c>
       <c r="B68" s="21" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C68" s="21" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.6">
@@ -4306,10 +4309,10 @@
         <v>66</v>
       </c>
       <c r="B69" s="21" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C69" s="21" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.6">
@@ -4317,10 +4320,10 @@
         <v>67</v>
       </c>
       <c r="B70" s="21" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C70" s="21" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.6">
@@ -4328,10 +4331,10 @@
         <v>68</v>
       </c>
       <c r="B71" s="21" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C71" s="21" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4339,10 +4342,10 @@
         <v>69</v>
       </c>
       <c r="B72" s="21" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C72" s="21" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4350,10 +4353,10 @@
         <v>70</v>
       </c>
       <c r="B73" s="21" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C73" s="21" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4361,10 +4364,10 @@
         <v>71</v>
       </c>
       <c r="B74" s="21" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C74" s="21" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4372,10 +4375,10 @@
         <v>72</v>
       </c>
       <c r="B75" s="21" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C75" s="21" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4383,10 +4386,10 @@
         <v>73</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.6">
@@ -4394,10 +4397,10 @@
         <v>74</v>
       </c>
       <c r="B77" s="21" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C77" s="21" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4405,10 +4408,10 @@
         <v>75</v>
       </c>
       <c r="B78" s="21" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C78" s="21" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.6">
@@ -4416,10 +4419,10 @@
         <v>76</v>
       </c>
       <c r="B79" s="21" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C79" s="21" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.6">
@@ -4427,10 +4430,10 @@
         <v>77</v>
       </c>
       <c r="B80" s="21" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C80" s="21" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.6">
@@ -4438,10 +4441,10 @@
         <v>78</v>
       </c>
       <c r="B81" s="21" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C81" s="21" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4449,10 +4452,10 @@
         <v>79</v>
       </c>
       <c r="B82" s="21" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C82" s="21" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.6">
@@ -4460,10 +4463,10 @@
         <v>80</v>
       </c>
       <c r="B83" s="21" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C83" s="21" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.6">
@@ -4471,10 +4474,10 @@
         <v>81</v>
       </c>
       <c r="B84" s="21" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C84" s="21" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4482,10 +4485,10 @@
         <v>82</v>
       </c>
       <c r="B85" s="21" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C85" s="21" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.6">
@@ -4493,10 +4496,10 @@
         <v>83</v>
       </c>
       <c r="B86" s="21" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C86" s="21" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.6">
@@ -4504,10 +4507,10 @@
         <v>84</v>
       </c>
       <c r="B87" s="21" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C87" s="21" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.6">
@@ -4515,10 +4518,10 @@
         <v>85</v>
       </c>
       <c r="B88" s="21" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C88" s="21" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.6">
@@ -4526,10 +4529,10 @@
         <v>86</v>
       </c>
       <c r="B89" s="21" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C89" s="21" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.6">
@@ -4537,10 +4540,10 @@
         <v>87</v>
       </c>
       <c r="B90" s="21" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C90" s="21" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.6">
@@ -4548,10 +4551,10 @@
         <v>88</v>
       </c>
       <c r="B91" s="21" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C91" s="21" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4559,10 +4562,10 @@
         <v>89</v>
       </c>
       <c r="B92" s="21" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C92" s="21" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4570,10 +4573,10 @@
         <v>90</v>
       </c>
       <c r="B93" s="21" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C93" s="21" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4581,10 +4584,10 @@
         <v>91</v>
       </c>
       <c r="B94" s="21" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C94" s="21" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.6">
@@ -4592,10 +4595,10 @@
         <v>92</v>
       </c>
       <c r="B95" s="21" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C95" s="21" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.6">
@@ -4603,10 +4606,10 @@
         <v>93</v>
       </c>
       <c r="B96" s="21" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="C96" s="21" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4614,10 +4617,10 @@
         <v>94</v>
       </c>
       <c r="B97" s="21" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C97" s="21" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.6">
@@ -4625,10 +4628,10 @@
         <v>95</v>
       </c>
       <c r="B98" s="21" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C98" s="21" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.6">
@@ -4636,10 +4639,10 @@
         <v>96</v>
       </c>
       <c r="B99" s="21" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C99" s="21" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.6">
@@ -4647,10 +4650,10 @@
         <v>97</v>
       </c>
       <c r="B100" s="21" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C100" s="21" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.6">
@@ -4658,10 +4661,10 @@
         <v>98</v>
       </c>
       <c r="B101" s="21" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C101" s="21" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.6">
@@ -4669,10 +4672,10 @@
         <v>99</v>
       </c>
       <c r="B102" s="21" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C102" s="21" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4680,10 +4683,10 @@
         <v>100</v>
       </c>
       <c r="B103" s="21" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C103" s="21" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.6">
@@ -4691,10 +4694,10 @@
         <v>101</v>
       </c>
       <c r="B104" s="21" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="C104" s="21" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.6">
@@ -4702,10 +4705,10 @@
         <v>102</v>
       </c>
       <c r="B105" s="21" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="C105" s="21" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.6">
@@ -4713,10 +4716,10 @@
         <v>103</v>
       </c>
       <c r="B106" s="21" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C106" s="21" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.6">
@@ -4724,10 +4727,10 @@
         <v>104</v>
       </c>
       <c r="B107" s="21" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="C107" s="21" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.6">
@@ -4735,10 +4738,10 @@
         <v>105</v>
       </c>
       <c r="B108" s="21" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="C108" s="21" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4746,10 +4749,10 @@
         <v>106</v>
       </c>
       <c r="B109" s="21" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C109" s="21" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.6">
@@ -4757,10 +4760,10 @@
         <v>107</v>
       </c>
       <c r="B110" s="21" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C110" s="21" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.6">
@@ -4768,10 +4771,10 @@
         <v>108</v>
       </c>
       <c r="B111" s="21" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C111" s="21" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.6">
@@ -4779,10 +4782,10 @@
         <v>109</v>
       </c>
       <c r="B112" s="21" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C112" s="21" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.6">
@@ -4790,10 +4793,10 @@
         <v>110</v>
       </c>
       <c r="B113" s="21" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="C113" s="21" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.6">
@@ -4801,10 +4804,10 @@
         <v>111</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="C114" s="21" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.6">
@@ -4812,10 +4815,10 @@
         <v>112</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C115" s="21" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.6">
@@ -4823,10 +4826,10 @@
         <v>113</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C116" s="21" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.6">
@@ -4834,10 +4837,10 @@
         <v>114</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="C117" s="21" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.6">
@@ -4845,10 +4848,10 @@
         <v>115</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C118" s="21" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.6">
@@ -4856,10 +4859,10 @@
         <v>116</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C119" s="21" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.6">
@@ -4867,10 +4870,10 @@
         <v>117</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.6">
@@ -4878,10 +4881,10 @@
         <v>118</v>
       </c>
       <c r="B121" s="21" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C121" s="21" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.6">
@@ -4889,10 +4892,10 @@
         <v>119</v>
       </c>
       <c r="B122" s="21" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C122" s="21" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.6">
@@ -4900,10 +4903,10 @@
         <v>120</v>
       </c>
       <c r="B123" s="21" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C123" s="21" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.6">
@@ -4911,10 +4914,10 @@
         <v>121</v>
       </c>
       <c r="B124" s="21" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C124" s="21" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.6">
@@ -4922,10 +4925,10 @@
         <v>122</v>
       </c>
       <c r="B125" s="21" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C125" s="21" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.6">
@@ -4933,10 +4936,10 @@
         <v>123</v>
       </c>
       <c r="B126" s="21" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C126" s="21" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.6">
@@ -4944,10 +4947,10 @@
         <v>124</v>
       </c>
       <c r="B127" s="21" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C127" s="21" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.6">
@@ -4955,10 +4958,10 @@
         <v>125</v>
       </c>
       <c r="B128" s="21" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C128" s="21" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/knto_images(현황).xlsx
+++ b/knto_images(현황).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\WebImages_travel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BA8804-6326-4C55-B793-BB4E1B6177E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2900DC59-EBC8-49EE-ADD1-C0EA36ECC75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6128" yWindow="60" windowWidth="14309" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4808" yWindow="667" windowWidth="14310" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="전체" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="419">
   <si>
     <t>여행지명</t>
   </si>
@@ -340,9 +340,6 @@
   </si>
   <si>
     <t>덕수궁: 덕수궁 3월 문화 행사와 주변 투어 (콘서트 일정, 카페 추천, 교통 가이드)</t>
-  </si>
-  <si>
-    <t>수문장 교대의식: 수문장 교대의식과 함께하는 3월 궁궐 데이트 (의상 설명, 사진 팁, 입장 정보)</t>
   </si>
   <si>
     <t xml:space="preserve">수문장 교대의식: 3월 수문장 교대의식 관람 가이드 (공연 시간표, 베스트 뷰 포인트, 주변 궁궐 연계)  </t>
@@ -1432,12 +1429,53 @@
     <t>경희궁: 경희궁에서 만나는 4월의 고즈넉한 매력 (봄 행사 일정, 주변 카페 추천, 사진 촬영 포인트)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>수문장 교대의식: 수문장 교대의식과 함께하는 4월 궁궐 데이트 (의상 설명, 사진 팁, 입장 정보)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>백해영갤러리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해방촌</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">백해영갤러리: 4월 백해영갤러리 전시 추천 &amp; 방문 가이드 (봄 전시 일정, 작품 감상 팁, 찾아가는 길) </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+백해영갤러리: 백해영갤러리에서 즐기는 감성 아트 데이트 (전시 테마, 카페 휴식 공간, 사진 촬영 포인트)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>해방촌</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">: 해방촌 골목 산책 &amp; 카페 투어 (봄 분위기 최고, 감성 카페 추천, 벽화 포인트) </t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>해방촌: 해방촌에서 즐기는 서울 데이트 코스 (야경 맛집, 숨은 맛집, 남산뷰 스팟 가이드)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1516,6 +1554,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1573,7 +1618,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1628,6 +1673,19 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1935,7 +1993,7 @@
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B3" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C3" s="2">
         <v>10</v>
@@ -1943,7 +2001,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B4" s="10" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C4" s="2">
         <v>9</v>
@@ -1951,7 +2009,7 @@
     </row>
     <row r="5" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B5" s="9" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C5" s="2">
         <v>8</v>
@@ -1959,7 +2017,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B6" s="9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" s="2">
         <v>8</v>
@@ -1967,7 +2025,7 @@
     </row>
     <row r="7" spans="2:3" x14ac:dyDescent="0.6">
       <c r="B7" s="10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2">
         <v>6</v>
@@ -2801,7 +2859,7 @@
         <v>9</v>
       </c>
       <c r="F2" s="12" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.6">
@@ -2815,7 +2873,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="25" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.6">
@@ -2855,7 +2913,7 @@
         <v>7</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.6">
@@ -2921,7 +2979,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.6">
@@ -2951,18 +3009,18 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.6">
       <c r="A14" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.6">
       <c r="B15" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C15" s="1">
         <v>6</v>
@@ -2973,7 +3031,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.6">
       <c r="B16" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" s="1">
         <v>6</v>
@@ -2981,31 +3039,39 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B17" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C17" s="1">
         <v>6</v>
       </c>
       <c r="F17" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
       <c r="F18" s="22" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
+      <c r="B19" s="26" t="s">
+        <v>413</v>
+      </c>
+      <c r="C19" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
+      <c r="B20" s="27" t="s">
+        <v>414</v>
+      </c>
+      <c r="C20" s="2">
+        <v>7</v>
+      </c>
       <c r="F20" s="11" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.6">
@@ -3023,14 +3089,14 @@
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
       <c r="F23" s="6" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="F24" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.6">
@@ -3041,14 +3107,14 @@
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="F26" s="22" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="F27" s="22" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.6">
@@ -3059,14 +3125,14 @@
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="F29" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="F30" s="1" t="s">
-        <v>103</v>
+        <v>412</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.6">
@@ -3077,7 +3143,7 @@
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="F32" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.6">
@@ -3088,7 +3154,7 @@
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="F34" s="13" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.6">
@@ -3100,7 +3166,7 @@
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="F36" s="15" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.6">
@@ -3112,7 +3178,7 @@
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="F38" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.6">
@@ -3124,7 +3190,7 @@
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="F40" s="15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.6">
@@ -3146,7 +3212,7 @@
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="F44" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.6">
@@ -3158,7 +3224,7 @@
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="F46" s="15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.6">
@@ -3170,7 +3236,7 @@
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="F48" s="15" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.6">
@@ -3182,7 +3248,7 @@
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="F50" s="15" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.6">
@@ -3204,7 +3270,7 @@
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="F54" s="13" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.6">
@@ -3216,7 +3282,7 @@
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="F56" s="23" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.6">
@@ -3228,7 +3294,7 @@
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="F58" s="23" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="59" spans="2:6" x14ac:dyDescent="0.6">
@@ -3240,86 +3306,98 @@
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="F60" s="23" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="61" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:6" ht="33.75" x14ac:dyDescent="0.6">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.6">
+      <c r="F62" s="28" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="63" spans="2:6" ht="50.65" x14ac:dyDescent="0.6">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
+      <c r="F63" s="29" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
-    </row>
-    <row r="65" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F64" s="30" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
-    </row>
-    <row r="66" spans="2:3" x14ac:dyDescent="0.6">
+      <c r="F65" s="22" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="67" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="68" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="69" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="70" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="71" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="72" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="73" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="74" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="75" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="76" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="77" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="78" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="79" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="80" spans="2:6" x14ac:dyDescent="0.6">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
     </row>
@@ -3429,131 +3507,131 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A1" t="s">
+        <v>131</v>
+      </c>
+      <c r="B1" t="s">
         <v>132</v>
       </c>
-      <c r="B1" t="s">
-        <v>133</v>
-      </c>
       <c r="C1" s="18" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E1" t="s">
         <v>135</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>136</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>137</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>141</v>
+      </c>
+      <c r="I1" t="s">
         <v>138</v>
-      </c>
-      <c r="H1" t="s">
-        <v>142</v>
-      </c>
-      <c r="I1" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D2" s="17">
         <v>107698</v>
       </c>
       <c r="E2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G2" t="s">
         <v>140</v>
-      </c>
-      <c r="G2" t="s">
-        <v>141</v>
       </c>
       <c r="H2" s="17">
         <v>2830</v>
       </c>
       <c r="I2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="J2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B4" t="s">
+        <v>399</v>
+      </c>
+      <c r="C4" s="18" t="s">
         <v>400</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>401</v>
       </c>
       <c r="D4" s="17">
         <v>122676</v>
       </c>
       <c r="F4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="G4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H4" s="17">
         <v>2420</v>
       </c>
       <c r="J4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.6">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D6" s="17">
         <v>107729</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F6" t="s">
+        <v>139</v>
+      </c>
+      <c r="G6" t="s">
         <v>140</v>
-      </c>
-      <c r="G6" t="s">
-        <v>141</v>
       </c>
       <c r="H6" s="17">
         <v>2930</v>
       </c>
       <c r="I6" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="J6" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -3575,18 +3653,18 @@
   <sheetData>
     <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.6">
       <c r="A1" s="19" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.6">
       <c r="A3" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="B3" s="20" t="s">
         <v>153</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="C3" s="20" t="s">
         <v>154</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.6">
@@ -3594,10 +3672,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="21" t="s">
+        <v>155</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>156</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.6">
@@ -3605,10 +3683,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>158</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.6">
@@ -3616,10 +3694,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="21" t="s">
+        <v>159</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>160</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.6">
@@ -3627,10 +3705,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="21" t="s">
+        <v>161</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>162</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.6">
@@ -3638,10 +3716,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C8" s="21" t="s">
         <v>164</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.6">
@@ -3649,10 +3727,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="21" t="s">
+        <v>165</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>166</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.6">
@@ -3660,10 +3738,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="21" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>168</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.6">
@@ -3671,10 +3749,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="21" t="s">
         <v>170</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.6">
@@ -3682,10 +3760,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="21" t="s">
+        <v>171</v>
+      </c>
+      <c r="C12" s="21" t="s">
         <v>172</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.6">
@@ -3693,10 +3771,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>174</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.6">
@@ -3704,10 +3782,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="21" t="s">
         <v>176</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.6">
@@ -3715,10 +3793,10 @@
         <v>12</v>
       </c>
       <c r="B15" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="21" t="s">
         <v>178</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.6">
@@ -3726,10 +3804,10 @@
         <v>13</v>
       </c>
       <c r="B16" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C16" s="21" t="s">
         <v>180</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.6">
@@ -3737,10 +3815,10 @@
         <v>14</v>
       </c>
       <c r="B17" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C17" s="21" t="s">
         <v>182</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.6">
@@ -3748,10 +3826,10 @@
         <v>15</v>
       </c>
       <c r="B18" s="21" t="s">
+        <v>183</v>
+      </c>
+      <c r="C18" s="21" t="s">
         <v>184</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.6">
@@ -3759,10 +3837,10 @@
         <v>16</v>
       </c>
       <c r="B19" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>186</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3770,10 +3848,10 @@
         <v>17</v>
       </c>
       <c r="B20" s="21" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20" s="21" t="s">
         <v>188</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3781,10 +3859,10 @@
         <v>18</v>
       </c>
       <c r="B21" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C21" s="21" t="s">
         <v>190</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3792,10 +3870,10 @@
         <v>19</v>
       </c>
       <c r="B22" s="21" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" s="21" t="s">
         <v>192</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.6">
@@ -3803,10 +3881,10 @@
         <v>20</v>
       </c>
       <c r="B23" s="21" t="s">
+        <v>193</v>
+      </c>
+      <c r="C23" s="21" t="s">
         <v>194</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.6">
@@ -3814,10 +3892,10 @@
         <v>21</v>
       </c>
       <c r="B24" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="C24" s="21" t="s">
         <v>196</v>
-      </c>
-      <c r="C24" s="21" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.6">
@@ -3825,10 +3903,10 @@
         <v>22</v>
       </c>
       <c r="B25" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="C25" s="21" t="s">
         <v>198</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.6">
@@ -3836,10 +3914,10 @@
         <v>23</v>
       </c>
       <c r="B26" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="C26" s="21" t="s">
         <v>200</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.6">
@@ -3847,10 +3925,10 @@
         <v>24</v>
       </c>
       <c r="B27" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C27" s="21" t="s">
         <v>202</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3858,10 +3936,10 @@
         <v>25</v>
       </c>
       <c r="B28" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="C28" s="21" t="s">
         <v>204</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.6">
@@ -3869,10 +3947,10 @@
         <v>26</v>
       </c>
       <c r="B29" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="C29" s="21" t="s">
         <v>206</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.6">
@@ -3880,10 +3958,10 @@
         <v>27</v>
       </c>
       <c r="B30" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>208</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3891,10 +3969,10 @@
         <v>28</v>
       </c>
       <c r="B31" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="C31" s="21" t="s">
         <v>210</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3902,10 +3980,10 @@
         <v>29</v>
       </c>
       <c r="B32" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="C32" s="21" t="s">
         <v>212</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3913,10 +3991,10 @@
         <v>30</v>
       </c>
       <c r="B33" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="C33" s="21" t="s">
         <v>214</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3924,10 +4002,10 @@
         <v>31</v>
       </c>
       <c r="B34" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="C34" s="21" t="s">
         <v>216</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.6">
@@ -3935,10 +4013,10 @@
         <v>32</v>
       </c>
       <c r="B35" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="C35" s="21" t="s">
         <v>218</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3946,10 +4024,10 @@
         <v>33</v>
       </c>
       <c r="B36" s="21" t="s">
+        <v>219</v>
+      </c>
+      <c r="C36" s="21" t="s">
         <v>220</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.6">
@@ -3957,10 +4035,10 @@
         <v>34</v>
       </c>
       <c r="B37" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="C37" s="21" t="s">
         <v>222</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3968,10 +4046,10 @@
         <v>35</v>
       </c>
       <c r="B38" s="21" t="s">
+        <v>223</v>
+      </c>
+      <c r="C38" s="21" t="s">
         <v>224</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3979,10 +4057,10 @@
         <v>36</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -3990,10 +4068,10 @@
         <v>37</v>
       </c>
       <c r="B40" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="C40" s="21" t="s">
         <v>227</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.6">
@@ -4001,10 +4079,10 @@
         <v>38</v>
       </c>
       <c r="B41" s="21" t="s">
+        <v>228</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>229</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.6">
@@ -4012,10 +4090,10 @@
         <v>39</v>
       </c>
       <c r="B42" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="C42" s="21" t="s">
         <v>231</v>
-      </c>
-      <c r="C42" s="21" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.6">
@@ -4023,10 +4101,10 @@
         <v>40</v>
       </c>
       <c r="B43" s="21" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>233</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.6">
@@ -4034,10 +4112,10 @@
         <v>41</v>
       </c>
       <c r="B44" s="21" t="s">
+        <v>234</v>
+      </c>
+      <c r="C44" s="21" t="s">
         <v>235</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.6">
@@ -4045,10 +4123,10 @@
         <v>42</v>
       </c>
       <c r="B45" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="C45" s="21" t="s">
         <v>237</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4056,10 +4134,10 @@
         <v>43</v>
       </c>
       <c r="B46" s="21" t="s">
+        <v>238</v>
+      </c>
+      <c r="C46" s="21" t="s">
         <v>239</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.6">
@@ -4067,10 +4145,10 @@
         <v>44</v>
       </c>
       <c r="B47" s="21" t="s">
+        <v>240</v>
+      </c>
+      <c r="C47" s="21" t="s">
         <v>241</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.6">
@@ -4078,10 +4156,10 @@
         <v>45</v>
       </c>
       <c r="B48" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="C48" s="21" t="s">
         <v>243</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.6">
@@ -4089,10 +4167,10 @@
         <v>46</v>
       </c>
       <c r="B49" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="C49" s="21" t="s">
         <v>245</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.6">
@@ -4100,10 +4178,10 @@
         <v>47</v>
       </c>
       <c r="B50" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="C50" s="21" t="s">
         <v>247</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.6">
@@ -4111,10 +4189,10 @@
         <v>48</v>
       </c>
       <c r="B51" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="C51" s="21" t="s">
         <v>249</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.6">
@@ -4122,10 +4200,10 @@
         <v>49</v>
       </c>
       <c r="B52" s="21" t="s">
+        <v>250</v>
+      </c>
+      <c r="C52" s="21" t="s">
         <v>251</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.6">
@@ -4133,10 +4211,10 @@
         <v>50</v>
       </c>
       <c r="B53" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="C53" s="21" t="s">
         <v>253</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.6">
@@ -4144,10 +4222,10 @@
         <v>51</v>
       </c>
       <c r="B54" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="C54" s="21" t="s">
         <v>255</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.6">
@@ -4155,10 +4233,10 @@
         <v>52</v>
       </c>
       <c r="B55" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="C55" s="21" t="s">
         <v>257</v>
-      </c>
-      <c r="C55" s="21" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.6">
@@ -4166,10 +4244,10 @@
         <v>53</v>
       </c>
       <c r="B56" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="C56" s="21" t="s">
         <v>259</v>
-      </c>
-      <c r="C56" s="21" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.6">
@@ -4177,10 +4255,10 @@
         <v>54</v>
       </c>
       <c r="B57" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="C57" s="21" t="s">
         <v>261</v>
-      </c>
-      <c r="C57" s="21" t="s">
-        <v>262</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.6">
@@ -4188,10 +4266,10 @@
         <v>55</v>
       </c>
       <c r="B58" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="C58" s="21" t="s">
         <v>263</v>
-      </c>
-      <c r="C58" s="21" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.6">
@@ -4199,10 +4277,10 @@
         <v>56</v>
       </c>
       <c r="B59" s="21" t="s">
+        <v>264</v>
+      </c>
+      <c r="C59" s="21" t="s">
         <v>265</v>
-      </c>
-      <c r="C59" s="21" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.6">
@@ -4210,10 +4288,10 @@
         <v>57</v>
       </c>
       <c r="B60" s="21" t="s">
+        <v>266</v>
+      </c>
+      <c r="C60" s="21" t="s">
         <v>267</v>
-      </c>
-      <c r="C60" s="21" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.6">
@@ -4221,10 +4299,10 @@
         <v>58</v>
       </c>
       <c r="B61" s="21" t="s">
+        <v>268</v>
+      </c>
+      <c r="C61" s="21" t="s">
         <v>269</v>
-      </c>
-      <c r="C61" s="21" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.6">
@@ -4232,10 +4310,10 @@
         <v>59</v>
       </c>
       <c r="B62" s="21" t="s">
+        <v>270</v>
+      </c>
+      <c r="C62" s="21" t="s">
         <v>271</v>
-      </c>
-      <c r="C62" s="21" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.6">
@@ -4243,10 +4321,10 @@
         <v>60</v>
       </c>
       <c r="B63" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="C63" s="21" t="s">
         <v>273</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4254,10 +4332,10 @@
         <v>61</v>
       </c>
       <c r="B64" s="21" t="s">
+        <v>274</v>
+      </c>
+      <c r="C64" s="21" t="s">
         <v>275</v>
-      </c>
-      <c r="C64" s="21" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4265,10 +4343,10 @@
         <v>62</v>
       </c>
       <c r="B65" s="21" t="s">
+        <v>276</v>
+      </c>
+      <c r="C65" s="21" t="s">
         <v>277</v>
-      </c>
-      <c r="C65" s="21" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4276,10 +4354,10 @@
         <v>63</v>
       </c>
       <c r="B66" s="21" t="s">
+        <v>278</v>
+      </c>
+      <c r="C66" s="21" t="s">
         <v>279</v>
-      </c>
-      <c r="C66" s="21" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.6">
@@ -4287,10 +4365,10 @@
         <v>64</v>
       </c>
       <c r="B67" s="21" t="s">
+        <v>280</v>
+      </c>
+      <c r="C67" s="21" t="s">
         <v>281</v>
-      </c>
-      <c r="C67" s="21" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.6">
@@ -4298,10 +4376,10 @@
         <v>65</v>
       </c>
       <c r="B68" s="21" t="s">
+        <v>282</v>
+      </c>
+      <c r="C68" s="21" t="s">
         <v>283</v>
-      </c>
-      <c r="C68" s="21" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.6">
@@ -4309,10 +4387,10 @@
         <v>66</v>
       </c>
       <c r="B69" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="C69" s="21" t="s">
         <v>285</v>
-      </c>
-      <c r="C69" s="21" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.6">
@@ -4320,10 +4398,10 @@
         <v>67</v>
       </c>
       <c r="B70" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="C70" s="21" t="s">
         <v>287</v>
-      </c>
-      <c r="C70" s="21" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.6">
@@ -4331,10 +4409,10 @@
         <v>68</v>
       </c>
       <c r="B71" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="C71" s="21" t="s">
         <v>289</v>
-      </c>
-      <c r="C71" s="21" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="72" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4342,10 +4420,10 @@
         <v>69</v>
       </c>
       <c r="B72" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="C72" s="21" t="s">
         <v>291</v>
-      </c>
-      <c r="C72" s="21" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="73" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4353,10 +4431,10 @@
         <v>70</v>
       </c>
       <c r="B73" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="C73" s="21" t="s">
         <v>293</v>
-      </c>
-      <c r="C73" s="21" t="s">
-        <v>294</v>
       </c>
     </row>
     <row r="74" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4364,10 +4442,10 @@
         <v>71</v>
       </c>
       <c r="B74" s="21" t="s">
+        <v>294</v>
+      </c>
+      <c r="C74" s="21" t="s">
         <v>295</v>
-      </c>
-      <c r="C74" s="21" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="75" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4375,10 +4453,10 @@
         <v>72</v>
       </c>
       <c r="B75" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="C75" s="21" t="s">
         <v>297</v>
-      </c>
-      <c r="C75" s="21" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="76" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4386,10 +4464,10 @@
         <v>73</v>
       </c>
       <c r="B76" s="21" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C76" s="21" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.6">
@@ -4397,10 +4475,10 @@
         <v>74</v>
       </c>
       <c r="B77" s="21" t="s">
+        <v>299</v>
+      </c>
+      <c r="C77" s="21" t="s">
         <v>300</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="78" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4408,10 +4486,10 @@
         <v>75</v>
       </c>
       <c r="B78" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="C78" s="21" t="s">
         <v>302</v>
-      </c>
-      <c r="C78" s="21" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.6">
@@ -4419,10 +4497,10 @@
         <v>76</v>
       </c>
       <c r="B79" s="21" t="s">
+        <v>303</v>
+      </c>
+      <c r="C79" s="21" t="s">
         <v>304</v>
-      </c>
-      <c r="C79" s="21" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.6">
@@ -4430,10 +4508,10 @@
         <v>77</v>
       </c>
       <c r="B80" s="21" t="s">
+        <v>305</v>
+      </c>
+      <c r="C80" s="21" t="s">
         <v>306</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.6">
@@ -4441,10 +4519,10 @@
         <v>78</v>
       </c>
       <c r="B81" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="C81" s="21" t="s">
         <v>308</v>
-      </c>
-      <c r="C81" s="21" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4452,10 +4530,10 @@
         <v>79</v>
       </c>
       <c r="B82" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="C82" s="21" t="s">
         <v>310</v>
-      </c>
-      <c r="C82" s="21" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.6">
@@ -4463,10 +4541,10 @@
         <v>80</v>
       </c>
       <c r="B83" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C83" s="21" t="s">
         <v>312</v>
-      </c>
-      <c r="C83" s="21" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.6">
@@ -4474,10 +4552,10 @@
         <v>81</v>
       </c>
       <c r="B84" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="C84" s="21" t="s">
         <v>314</v>
-      </c>
-      <c r="C84" s="21" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4485,10 +4563,10 @@
         <v>82</v>
       </c>
       <c r="B85" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="C85" s="21" t="s">
         <v>316</v>
-      </c>
-      <c r="C85" s="21" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.6">
@@ -4496,10 +4574,10 @@
         <v>83</v>
       </c>
       <c r="B86" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="C86" s="21" t="s">
         <v>318</v>
-      </c>
-      <c r="C86" s="21" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.6">
@@ -4507,10 +4585,10 @@
         <v>84</v>
       </c>
       <c r="B87" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="C87" s="21" t="s">
         <v>320</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.6">
@@ -4518,10 +4596,10 @@
         <v>85</v>
       </c>
       <c r="B88" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="C88" s="21" t="s">
         <v>322</v>
-      </c>
-      <c r="C88" s="21" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.6">
@@ -4529,10 +4607,10 @@
         <v>86</v>
       </c>
       <c r="B89" s="21" t="s">
+        <v>323</v>
+      </c>
+      <c r="C89" s="21" t="s">
         <v>324</v>
-      </c>
-      <c r="C89" s="21" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.6">
@@ -4540,10 +4618,10 @@
         <v>87</v>
       </c>
       <c r="B90" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C90" s="21" t="s">
         <v>326</v>
-      </c>
-      <c r="C90" s="21" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.6">
@@ -4551,10 +4629,10 @@
         <v>88</v>
       </c>
       <c r="B91" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C91" s="21" t="s">
         <v>328</v>
-      </c>
-      <c r="C91" s="21" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4562,10 +4640,10 @@
         <v>89</v>
       </c>
       <c r="B92" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C92" s="21" t="s">
         <v>330</v>
-      </c>
-      <c r="C92" s="21" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4573,10 +4651,10 @@
         <v>90</v>
       </c>
       <c r="B93" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C93" s="21" t="s">
         <v>330</v>
-      </c>
-      <c r="C93" s="21" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4584,10 +4662,10 @@
         <v>91</v>
       </c>
       <c r="B94" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="C94" s="21" t="s">
         <v>330</v>
-      </c>
-      <c r="C94" s="21" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.6">
@@ -4595,10 +4673,10 @@
         <v>92</v>
       </c>
       <c r="B95" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="C95" s="21" t="s">
         <v>332</v>
-      </c>
-      <c r="C95" s="21" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.6">
@@ -4606,10 +4684,10 @@
         <v>93</v>
       </c>
       <c r="B96" s="21" t="s">
+        <v>333</v>
+      </c>
+      <c r="C96" s="21" t="s">
         <v>334</v>
-      </c>
-      <c r="C96" s="21" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4617,10 +4695,10 @@
         <v>94</v>
       </c>
       <c r="B97" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="C97" s="21" t="s">
         <v>336</v>
-      </c>
-      <c r="C97" s="21" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.6">
@@ -4628,10 +4706,10 @@
         <v>95</v>
       </c>
       <c r="B98" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="C98" s="21" t="s">
         <v>338</v>
-      </c>
-      <c r="C98" s="21" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.6">
@@ -4639,10 +4717,10 @@
         <v>96</v>
       </c>
       <c r="B99" s="21" t="s">
+        <v>339</v>
+      </c>
+      <c r="C99" s="21" t="s">
         <v>340</v>
-      </c>
-      <c r="C99" s="21" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.6">
@@ -4650,10 +4728,10 @@
         <v>97</v>
       </c>
       <c r="B100" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="C100" s="21" t="s">
         <v>342</v>
-      </c>
-      <c r="C100" s="21" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.6">
@@ -4661,10 +4739,10 @@
         <v>98</v>
       </c>
       <c r="B101" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="C101" s="21" t="s">
         <v>344</v>
-      </c>
-      <c r="C101" s="21" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.6">
@@ -4672,10 +4750,10 @@
         <v>99</v>
       </c>
       <c r="B102" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="C102" s="21" t="s">
         <v>346</v>
-      </c>
-      <c r="C102" s="21" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4683,10 +4761,10 @@
         <v>100</v>
       </c>
       <c r="B103" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="C103" s="21" t="s">
         <v>348</v>
-      </c>
-      <c r="C103" s="21" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.6">
@@ -4694,10 +4772,10 @@
         <v>101</v>
       </c>
       <c r="B104" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="C104" s="21" t="s">
         <v>350</v>
-      </c>
-      <c r="C104" s="21" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.6">
@@ -4705,10 +4783,10 @@
         <v>102</v>
       </c>
       <c r="B105" s="21" t="s">
+        <v>351</v>
+      </c>
+      <c r="C105" s="21" t="s">
         <v>352</v>
-      </c>
-      <c r="C105" s="21" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.6">
@@ -4716,10 +4794,10 @@
         <v>103</v>
       </c>
       <c r="B106" s="21" t="s">
+        <v>353</v>
+      </c>
+      <c r="C106" s="21" t="s">
         <v>354</v>
-      </c>
-      <c r="C106" s="21" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.6">
@@ -4727,10 +4805,10 @@
         <v>104</v>
       </c>
       <c r="B107" s="21" t="s">
+        <v>355</v>
+      </c>
+      <c r="C107" s="21" t="s">
         <v>356</v>
-      </c>
-      <c r="C107" s="21" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.6">
@@ -4738,10 +4816,10 @@
         <v>105</v>
       </c>
       <c r="B108" s="21" t="s">
+        <v>357</v>
+      </c>
+      <c r="C108" s="21" t="s">
         <v>358</v>
-      </c>
-      <c r="C108" s="21" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="27" x14ac:dyDescent="0.6">
@@ -4749,10 +4827,10 @@
         <v>106</v>
       </c>
       <c r="B109" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="C109" s="21" t="s">
         <v>360</v>
-      </c>
-      <c r="C109" s="21" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.6">
@@ -4760,10 +4838,10 @@
         <v>107</v>
       </c>
       <c r="B110" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="C110" s="21" t="s">
         <v>362</v>
-      </c>
-      <c r="C110" s="21" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.6">
@@ -4771,10 +4849,10 @@
         <v>108</v>
       </c>
       <c r="B111" s="21" t="s">
+        <v>363</v>
+      </c>
+      <c r="C111" s="21" t="s">
         <v>364</v>
-      </c>
-      <c r="C111" s="21" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.6">
@@ -4782,10 +4860,10 @@
         <v>109</v>
       </c>
       <c r="B112" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="C112" s="21" t="s">
         <v>366</v>
-      </c>
-      <c r="C112" s="21" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.6">
@@ -4793,10 +4871,10 @@
         <v>110</v>
       </c>
       <c r="B113" s="21" t="s">
+        <v>367</v>
+      </c>
+      <c r="C113" s="21" t="s">
         <v>368</v>
-      </c>
-      <c r="C113" s="21" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.6">
@@ -4804,10 +4882,10 @@
         <v>111</v>
       </c>
       <c r="B114" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="C114" s="21" t="s">
         <v>370</v>
-      </c>
-      <c r="C114" s="21" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.6">
@@ -4815,10 +4893,10 @@
         <v>112</v>
       </c>
       <c r="B115" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="C115" s="21" t="s">
         <v>372</v>
-      </c>
-      <c r="C115" s="21" t="s">
-        <v>373</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.6">
@@ -4826,10 +4904,10 @@
         <v>113</v>
       </c>
       <c r="B116" s="21" t="s">
+        <v>373</v>
+      </c>
+      <c r="C116" s="21" t="s">
         <v>374</v>
-      </c>
-      <c r="C116" s="21" t="s">
-        <v>375</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.6">
@@ -4837,10 +4915,10 @@
         <v>114</v>
       </c>
       <c r="B117" s="21" t="s">
+        <v>375</v>
+      </c>
+      <c r="C117" s="21" t="s">
         <v>376</v>
-      </c>
-      <c r="C117" s="21" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.6">
@@ -4848,10 +4926,10 @@
         <v>115</v>
       </c>
       <c r="B118" s="21" t="s">
+        <v>377</v>
+      </c>
+      <c r="C118" s="21" t="s">
         <v>378</v>
-      </c>
-      <c r="C118" s="21" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.6">
@@ -4859,10 +4937,10 @@
         <v>116</v>
       </c>
       <c r="B119" s="21" t="s">
+        <v>379</v>
+      </c>
+      <c r="C119" s="21" t="s">
         <v>380</v>
-      </c>
-      <c r="C119" s="21" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.6">
@@ -4870,10 +4948,10 @@
         <v>117</v>
       </c>
       <c r="B120" s="21" t="s">
+        <v>381</v>
+      </c>
+      <c r="C120" s="21" t="s">
         <v>382</v>
-      </c>
-      <c r="C120" s="21" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.6">
@@ -4881,10 +4959,10 @@
         <v>118</v>
       </c>
       <c r="B121" s="21" t="s">
+        <v>383</v>
+      </c>
+      <c r="C121" s="21" t="s">
         <v>384</v>
-      </c>
-      <c r="C121" s="21" t="s">
-        <v>385</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.6">
@@ -4892,10 +4970,10 @@
         <v>119</v>
       </c>
       <c r="B122" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="C122" s="21" t="s">
         <v>386</v>
-      </c>
-      <c r="C122" s="21" t="s">
-        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.6">
@@ -4903,10 +4981,10 @@
         <v>120</v>
       </c>
       <c r="B123" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="C123" s="21" t="s">
         <v>388</v>
-      </c>
-      <c r="C123" s="21" t="s">
-        <v>389</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.6">
@@ -4914,10 +4992,10 @@
         <v>121</v>
       </c>
       <c r="B124" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="C124" s="21" t="s">
         <v>390</v>
-      </c>
-      <c r="C124" s="21" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.6">
@@ -4925,10 +5003,10 @@
         <v>122</v>
       </c>
       <c r="B125" s="21" t="s">
+        <v>391</v>
+      </c>
+      <c r="C125" s="21" t="s">
         <v>392</v>
-      </c>
-      <c r="C125" s="21" t="s">
-        <v>393</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.6">
@@ -4936,10 +5014,10 @@
         <v>123</v>
       </c>
       <c r="B126" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="C126" s="21" t="s">
         <v>394</v>
-      </c>
-      <c r="C126" s="21" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.6">
@@ -4947,10 +5025,10 @@
         <v>124</v>
       </c>
       <c r="B127" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="C127" s="21" t="s">
         <v>396</v>
-      </c>
-      <c r="C127" s="21" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.6">
@@ -4958,10 +5036,10 @@
         <v>125</v>
       </c>
       <c r="B128" s="21" t="s">
+        <v>397</v>
+      </c>
+      <c r="C128" s="21" t="s">
         <v>398</v>
-      </c>
-      <c r="C128" s="21" t="s">
-        <v>399</v>
       </c>
     </row>
   </sheetData>

--- a/knto_images(현황).xlsx
+++ b/knto_images(현황).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\WebImages_travel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2900DC59-EBC8-49EE-ADD1-C0EA36ECC75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A17089-4E6A-436C-A492-A20A667B4C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4808" yWindow="667" windowWidth="14310" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4470" yWindow="660" windowWidth="14310" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="전체" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="419">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="422">
   <si>
     <t>여행지명</t>
   </si>
@@ -1470,12 +1470,22 @@
     <t>해방촌: 해방촌에서 즐기는 서울 데이트 코스 (야경 맛집, 숨은 맛집, 남산뷰 스팟 가이드)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>여의도한강공원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뚝섬한강공원</t>
+  </si>
+  <si>
+    <t>한강드론공원</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1561,6 +1571,27 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF333333"/>
+      <name val="Pretendard GOV"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1618,7 +1649,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1673,12 +1704,6 @@
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1686,6 +1711,21 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -1967,7 +2007,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C101"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="24.75" style="1" customWidth="1"/>
@@ -1975,7 +2015,7 @@
     <col min="4" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:3">
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1983,7 +2023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:3">
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
@@ -1991,7 +2031,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:3">
       <c r="B3" s="9" t="s">
         <v>111</v>
       </c>
@@ -1999,7 +2039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:3">
       <c r="B4" s="10" t="s">
         <v>112</v>
       </c>
@@ -2007,7 +2047,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="5" spans="2:3">
       <c r="B5" s="9" t="s">
         <v>113</v>
       </c>
@@ -2015,7 +2055,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="6" spans="2:3">
       <c r="B6" s="9" t="s">
         <v>114</v>
       </c>
@@ -2023,7 +2063,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:3">
       <c r="B7" s="10" t="s">
         <v>115</v>
       </c>
@@ -2031,7 +2071,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:3">
       <c r="B8" s="2" t="s">
         <v>3</v>
       </c>
@@ -2039,7 +2079,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:3">
       <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
@@ -2047,7 +2087,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="10" spans="2:3">
       <c r="B10" s="2" t="s">
         <v>5</v>
       </c>
@@ -2055,7 +2095,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="11" spans="2:3">
       <c r="B11" s="2" t="s">
         <v>6</v>
       </c>
@@ -2063,7 +2103,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="12" spans="2:3">
       <c r="B12" s="2" t="s">
         <v>7</v>
       </c>
@@ -2071,7 +2111,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="13" spans="2:3">
       <c r="B13" s="2" t="s">
         <v>8</v>
       </c>
@@ -2079,7 +2119,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="14" spans="2:3">
       <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
@@ -2087,7 +2127,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="15" spans="2:3">
       <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
@@ -2095,7 +2135,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="16" spans="2:3">
       <c r="B16" s="2" t="s">
         <v>11</v>
       </c>
@@ -2103,7 +2143,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:3">
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
@@ -2111,7 +2151,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:3">
       <c r="B18" s="2" t="s">
         <v>13</v>
       </c>
@@ -2119,7 +2159,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:3">
       <c r="B19" s="2" t="s">
         <v>14</v>
       </c>
@@ -2127,7 +2167,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:3">
       <c r="B20" s="2" t="s">
         <v>15</v>
       </c>
@@ -2135,7 +2175,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:3">
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
@@ -2143,7 +2183,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:3">
       <c r="B22" s="2" t="s">
         <v>17</v>
       </c>
@@ -2151,7 +2191,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:3">
       <c r="B23" s="2" t="s">
         <v>18</v>
       </c>
@@ -2159,7 +2199,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:3">
       <c r="B24" s="2" t="s">
         <v>19</v>
       </c>
@@ -2167,7 +2207,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:3">
       <c r="B25" s="2" t="s">
         <v>20</v>
       </c>
@@ -2175,7 +2215,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:3">
       <c r="B26" s="2" t="s">
         <v>21</v>
       </c>
@@ -2183,7 +2223,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:3">
       <c r="B27" s="2" t="s">
         <v>22</v>
       </c>
@@ -2191,7 +2231,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:3">
       <c r="B28" s="2" t="s">
         <v>23</v>
       </c>
@@ -2199,7 +2239,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:3">
       <c r="B29" s="2" t="s">
         <v>24</v>
       </c>
@@ -2207,7 +2247,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:3">
       <c r="B30" s="2" t="s">
         <v>25</v>
       </c>
@@ -2215,7 +2255,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:3">
       <c r="B31" s="2" t="s">
         <v>26</v>
       </c>
@@ -2223,7 +2263,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:3">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -2234,7 +2274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:3">
       <c r="B33" s="2" t="s">
         <v>28</v>
       </c>
@@ -2242,7 +2282,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:3">
       <c r="B34" s="2" t="s">
         <v>29</v>
       </c>
@@ -2250,7 +2290,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:3">
       <c r="A35" s="1">
         <v>1</v>
       </c>
@@ -2261,7 +2301,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:3">
       <c r="B36" s="2" t="s">
         <v>31</v>
       </c>
@@ -2269,7 +2309,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:3">
       <c r="B37" s="2" t="s">
         <v>32</v>
       </c>
@@ -2277,7 +2317,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:3">
       <c r="B38" s="2" t="s">
         <v>33</v>
       </c>
@@ -2285,7 +2325,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:3">
       <c r="A39" s="1">
         <v>1</v>
       </c>
@@ -2296,7 +2336,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:3">
       <c r="B40" s="2" t="s">
         <v>35</v>
       </c>
@@ -2304,7 +2344,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:3">
       <c r="B41" s="2" t="s">
         <v>36</v>
       </c>
@@ -2312,7 +2352,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:3">
       <c r="B42" s="2" t="s">
         <v>37</v>
       </c>
@@ -2320,7 +2360,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:3">
       <c r="B43" s="2" t="s">
         <v>38</v>
       </c>
@@ -2328,7 +2368,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:3">
       <c r="B44" s="2" t="s">
         <v>39</v>
       </c>
@@ -2336,7 +2376,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:3">
       <c r="B45" s="2" t="s">
         <v>40</v>
       </c>
@@ -2344,7 +2384,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:3">
       <c r="B46" s="2" t="s">
         <v>41</v>
       </c>
@@ -2352,7 +2392,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:3">
       <c r="B47" s="2" t="s">
         <v>42</v>
       </c>
@@ -2360,7 +2400,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:3">
       <c r="A48" s="1">
         <v>1</v>
       </c>
@@ -2371,7 +2411,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:3">
       <c r="B49" s="2" t="s">
         <v>44</v>
       </c>
@@ -2379,7 +2419,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:3">
       <c r="A50" s="1">
         <v>1</v>
       </c>
@@ -2390,7 +2430,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:3">
       <c r="B51" s="2" t="s">
         <v>46</v>
       </c>
@@ -2398,7 +2438,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:3">
       <c r="A52" s="1">
         <v>1</v>
       </c>
@@ -2409,7 +2449,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:3">
       <c r="B53" s="2" t="s">
         <v>48</v>
       </c>
@@ -2417,7 +2457,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:3">
       <c r="B54" s="2" t="s">
         <v>49</v>
       </c>
@@ -2425,7 +2465,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:3">
       <c r="B55" s="2" t="s">
         <v>50</v>
       </c>
@@ -2433,7 +2473,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:3">
       <c r="B56" s="2" t="s">
         <v>51</v>
       </c>
@@ -2441,7 +2481,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:3">
       <c r="B57" s="2" t="s">
         <v>52</v>
       </c>
@@ -2449,7 +2489,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:3">
       <c r="B58" s="2" t="s">
         <v>53</v>
       </c>
@@ -2457,7 +2497,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:3">
       <c r="A59" s="1">
         <v>1</v>
       </c>
@@ -2468,7 +2508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:3">
       <c r="B60" s="2" t="s">
         <v>55</v>
       </c>
@@ -2476,7 +2516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:3">
       <c r="B61" s="2" t="s">
         <v>56</v>
       </c>
@@ -2484,7 +2524,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:3">
       <c r="B62" s="2" t="s">
         <v>57</v>
       </c>
@@ -2492,7 +2532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:3">
       <c r="B63" s="2" t="s">
         <v>58</v>
       </c>
@@ -2500,7 +2540,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:3">
       <c r="B64" s="2" t="s">
         <v>59</v>
       </c>
@@ -2508,7 +2548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:3">
       <c r="B65" s="2" t="s">
         <v>60</v>
       </c>
@@ -2516,7 +2556,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:3">
       <c r="B66" s="2" t="s">
         <v>61</v>
       </c>
@@ -2524,7 +2564,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:3">
       <c r="B67" s="2" t="s">
         <v>62</v>
       </c>
@@ -2532,7 +2572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:3">
       <c r="B68" s="2" t="s">
         <v>63</v>
       </c>
@@ -2540,7 +2580,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:3">
       <c r="A69" s="1">
         <v>1</v>
       </c>
@@ -2551,7 +2591,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:3">
       <c r="B70" s="2" t="s">
         <v>65</v>
       </c>
@@ -2559,7 +2599,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:3">
       <c r="B71" s="2" t="s">
         <v>66</v>
       </c>
@@ -2567,7 +2607,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:3">
       <c r="B72" s="2" t="s">
         <v>67</v>
       </c>
@@ -2575,7 +2615,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:3">
       <c r="B73" s="2" t="s">
         <v>68</v>
       </c>
@@ -2583,7 +2623,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:3">
       <c r="B74" s="2" t="s">
         <v>69</v>
       </c>
@@ -2591,7 +2631,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:3">
       <c r="B75" s="2" t="s">
         <v>70</v>
       </c>
@@ -2599,7 +2639,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:3">
       <c r="A76" s="1">
         <v>1</v>
       </c>
@@ -2610,7 +2650,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:3">
       <c r="B77" s="2" t="s">
         <v>72</v>
       </c>
@@ -2618,7 +2658,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:3">
       <c r="B78" s="2" t="s">
         <v>73</v>
       </c>
@@ -2626,7 +2666,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:3">
       <c r="B79" s="2" t="s">
         <v>74</v>
       </c>
@@ -2634,7 +2674,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:3">
       <c r="B80" s="2" t="s">
         <v>75</v>
       </c>
@@ -2642,7 +2682,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:3">
       <c r="B81" s="2" t="s">
         <v>76</v>
       </c>
@@ -2650,7 +2690,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:3">
       <c r="B82" s="2" t="s">
         <v>77</v>
       </c>
@@ -2658,7 +2698,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:3">
       <c r="B83" s="2" t="s">
         <v>78</v>
       </c>
@@ -2666,7 +2706,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:3">
       <c r="B84" s="2" t="s">
         <v>79</v>
       </c>
@@ -2674,7 +2714,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:3">
       <c r="B85" s="2" t="s">
         <v>80</v>
       </c>
@@ -2682,7 +2722,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:3">
       <c r="B86" s="2" t="s">
         <v>81</v>
       </c>
@@ -2690,7 +2730,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:3">
       <c r="B87" s="2" t="s">
         <v>82</v>
       </c>
@@ -2698,7 +2738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:3">
       <c r="B88" s="2" t="s">
         <v>83</v>
       </c>
@@ -2706,7 +2746,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:3">
       <c r="B89" s="2" t="s">
         <v>84</v>
       </c>
@@ -2714,7 +2754,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:3">
       <c r="B90" s="2" t="s">
         <v>85</v>
       </c>
@@ -2722,7 +2762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:3">
       <c r="B91" s="2" t="s">
         <v>86</v>
       </c>
@@ -2730,7 +2770,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:3">
       <c r="B92" s="2" t="s">
         <v>87</v>
       </c>
@@ -2738,7 +2778,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:3">
       <c r="B93" s="2" t="s">
         <v>88</v>
       </c>
@@ -2746,7 +2786,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:3">
       <c r="A94" s="1">
         <v>1</v>
       </c>
@@ -2757,7 +2797,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:3">
       <c r="B95" s="2" t="s">
         <v>90</v>
       </c>
@@ -2765,7 +2805,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:3">
       <c r="B96" s="2" t="s">
         <v>91</v>
       </c>
@@ -2773,7 +2813,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:3">
       <c r="B97" s="2" t="s">
         <v>92</v>
       </c>
@@ -2781,7 +2821,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:3">
       <c r="A98" s="1">
         <v>1</v>
       </c>
@@ -2792,7 +2832,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:3">
       <c r="B99" s="2" t="s">
         <v>94</v>
       </c>
@@ -2800,7 +2840,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:3">
       <c r="B100" s="2" t="s">
         <v>95</v>
       </c>
@@ -2808,7 +2848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:3">
       <c r="A101" s="1">
         <v>1</v>
       </c>
@@ -2829,7 +2869,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F05010-FAED-41D9-AC86-A7A9CDE8E2F2}">
   <dimension ref="A1:F101"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
     <col min="2" max="2" width="24.75" style="1" customWidth="1"/>
@@ -2839,7 +2879,7 @@
     <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:6">
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
@@ -2848,7 +2888,7 @@
       </c>
       <c r="F1"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:6">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -2862,7 +2902,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:6">
       <c r="A3" s="4">
         <v>1</v>
       </c>
@@ -2876,7 +2916,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:6">
       <c r="A4" s="4">
         <v>1</v>
       </c>
@@ -2888,7 +2928,7 @@
       </c>
       <c r="F4"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:6">
       <c r="A5" s="4">
         <v>1</v>
       </c>
@@ -2902,7 +2942,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:6">
       <c r="A6" s="4">
         <v>1</v>
       </c>
@@ -2916,7 +2956,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:6">
       <c r="A7" s="4">
         <v>1</v>
       </c>
@@ -2928,7 +2968,7 @@
       </c>
       <c r="F7"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:6">
       <c r="A8" s="4">
         <v>1</v>
       </c>
@@ -2942,7 +2982,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:6">
       <c r="A9" s="4">
         <v>1</v>
       </c>
@@ -2956,7 +2996,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:6">
       <c r="A10" s="4">
         <v>1</v>
       </c>
@@ -2968,7 +3008,7 @@
       </c>
       <c r="F10"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:6">
       <c r="A11" s="4">
         <v>1</v>
       </c>
@@ -2982,7 +3022,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:6">
       <c r="A12" s="4">
         <v>1</v>
       </c>
@@ -2996,7 +3036,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:6">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -3007,19 +3047,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:6">
       <c r="A14" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="4" t="s">
         <v>104</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B15" s="1" t="s">
+    <row r="15" spans="1:6">
+      <c r="B15" s="4" t="s">
         <v>105</v>
       </c>
       <c r="C15" s="1">
@@ -3029,16 +3069,16 @@
         <v>101</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.6">
-      <c r="B16" s="1" t="s">
+    <row r="16" spans="1:6">
+      <c r="B16" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C16" s="1">
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B17" s="1" t="s">
+    <row r="17" spans="2:6">
+      <c r="B17" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C17" s="1">
@@ -3048,23 +3088,23 @@
         <v>129</v>
       </c>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B18" s="2"/>
+    <row r="18" spans="2:6">
+      <c r="B18" s="5"/>
       <c r="C18" s="2"/>
       <c r="F18" s="22" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B19" s="26" t="s">
+    <row r="19" spans="2:6">
+      <c r="B19" s="31" t="s">
         <v>413</v>
       </c>
       <c r="C19" s="2">
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B20" s="27" t="s">
+    <row r="20" spans="2:6">
+      <c r="B20" s="32" t="s">
         <v>414</v>
       </c>
       <c r="C20" s="2">
@@ -3074,414 +3114,426 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+    <row r="21" spans="2:6">
+      <c r="B21" s="29" t="s">
+        <v>419</v>
+      </c>
+      <c r="C21" s="2">
+        <v>4</v>
+      </c>
       <c r="F21" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.6">
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
+    <row r="22" spans="2:6">
+      <c r="B22" s="30" t="s">
+        <v>420</v>
+      </c>
+      <c r="C22" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" ht="17.649999999999999">
+      <c r="B23" s="33" t="s">
+        <v>421</v>
+      </c>
+      <c r="C23" s="2">
+        <v>5</v>
+      </c>
       <c r="F23" s="6" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="24" spans="2:6">
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="F24" s="4" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="25" spans="2:6">
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="26" spans="2:6">
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
       <c r="F26" s="22" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="27" spans="2:6">
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
       <c r="F27" s="22" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="28" spans="2:6">
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="29" spans="2:6">
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
       <c r="F29" s="7" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="30" spans="2:6">
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
       <c r="F30" s="1" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="31" spans="2:6">
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="32" spans="2:6">
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
       <c r="F32" s="11" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="33" spans="2:6">
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="2:6" ht="27" x14ac:dyDescent="0.6">
+    <row r="34" spans="2:6" ht="27">
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
       <c r="F34" s="13" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="35" spans="2:6">
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
       <c r="F35" s="14"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="36" spans="2:6">
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="F36" s="15" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="37" spans="2:6">
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
       <c r="F37" s="14"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="38" spans="2:6">
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
       <c r="F38" s="15" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="39" spans="2:6">
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
       <c r="F39" s="16"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="40" spans="2:6">
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
       <c r="F40" s="15" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="41" spans="2:6">
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
       <c r="F41"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="42" spans="2:6">
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
       <c r="F42"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="43" spans="2:6">
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
       <c r="F43"/>
     </row>
-    <row r="44" spans="2:6" ht="27" x14ac:dyDescent="0.6">
+    <row r="44" spans="2:6" ht="27">
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
       <c r="F44" s="13" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="45" spans="2:6">
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
       <c r="F45" s="14"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="46" spans="2:6">
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
       <c r="F46" s="15" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="47" spans="2:6">
       <c r="B47" s="2"/>
       <c r="C47" s="2"/>
       <c r="F47" s="16"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="48" spans="2:6">
       <c r="B48" s="2"/>
       <c r="C48" s="2"/>
       <c r="F48" s="15" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="49" spans="2:6">
       <c r="B49" s="2"/>
       <c r="C49" s="2"/>
       <c r="F49" s="16"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="50" spans="2:6">
       <c r="B50" s="2"/>
       <c r="C50" s="2"/>
       <c r="F50" s="15" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="51" spans="2:6">
       <c r="B51" s="2"/>
       <c r="C51" s="2"/>
       <c r="F51"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="52" spans="2:6">
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="F52"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="53" spans="2:6">
       <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="F53"/>
     </row>
-    <row r="54" spans="2:6" ht="27" x14ac:dyDescent="0.6">
+    <row r="54" spans="2:6" ht="27">
       <c r="B54" s="2"/>
       <c r="C54" s="2"/>
       <c r="F54" s="13" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="55" spans="2:6">
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="F55" s="14"/>
     </row>
-    <row r="56" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="56" spans="2:6">
       <c r="B56" s="2"/>
       <c r="C56" s="2"/>
       <c r="F56" s="23" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="57" spans="2:6">
       <c r="B57" s="2"/>
       <c r="C57" s="2"/>
       <c r="F57" s="24"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="58" spans="2:6">
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
       <c r="F58" s="23" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="59" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="59" spans="2:6">
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
       <c r="F59" s="24"/>
     </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="60" spans="2:6">
       <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="F60" s="23" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="61" spans="2:6">
       <c r="B61" s="2"/>
       <c r="C61" s="2"/>
     </row>
-    <row r="62" spans="2:6" ht="33.75" x14ac:dyDescent="0.6">
+    <row r="62" spans="2:6" ht="33.75">
       <c r="B62" s="2"/>
       <c r="C62" s="2"/>
-      <c r="F62" s="28" t="s">
+      <c r="F62" s="26" t="s">
         <v>415</v>
       </c>
     </row>
-    <row r="63" spans="2:6" ht="50.65" x14ac:dyDescent="0.6">
+    <row r="63" spans="2:6" ht="50.65">
       <c r="B63" s="2"/>
       <c r="C63" s="2"/>
-      <c r="F63" s="29" t="s">
+      <c r="F63" s="27" t="s">
         <v>416</v>
       </c>
     </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="64" spans="2:6">
       <c r="B64" s="2"/>
       <c r="C64" s="2"/>
-      <c r="F64" s="30" t="s">
+      <c r="F64" s="28" t="s">
         <v>417</v>
       </c>
     </row>
-    <row r="65" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="65" spans="2:6">
       <c r="B65" s="2"/>
       <c r="C65" s="2"/>
       <c r="F65" s="22" t="s">
         <v>418</v>
       </c>
     </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="66" spans="2:6">
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="67" spans="2:6">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
     </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="68" spans="2:6">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
     </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="69" spans="2:6">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
     </row>
-    <row r="70" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="70" spans="2:6">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
     </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="71" spans="2:6">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
     </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="72" spans="2:6">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
     </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="73" spans="2:6">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
     </row>
-    <row r="74" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="74" spans="2:6">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
     </row>
-    <row r="75" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="75" spans="2:6">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
     </row>
-    <row r="76" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="76" spans="2:6">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
     </row>
-    <row r="77" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="77" spans="2:6">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
     </row>
-    <row r="78" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="78" spans="2:6">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
     </row>
-    <row r="79" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="79" spans="2:6">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
     </row>
-    <row r="80" spans="2:6" x14ac:dyDescent="0.6">
+    <row r="80" spans="2:6">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="81" spans="2:3">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="82" spans="2:3">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="83" spans="2:3">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="84" spans="2:3">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="85" spans="2:3">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="86" spans="2:3">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="87" spans="2:3">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="88" spans="2:3">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="89" spans="2:3">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
     </row>
-    <row r="90" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="90" spans="2:3">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="91" spans="2:3">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
     </row>
-    <row r="92" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="92" spans="2:3">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
     </row>
-    <row r="93" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="93" spans="2:3">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
     </row>
-    <row r="94" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="94" spans="2:3">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
     </row>
-    <row r="95" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="95" spans="2:3">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
     </row>
-    <row r="96" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="96" spans="2:3">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
     </row>
-    <row r="97" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="97" spans="2:3">
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
     </row>
-    <row r="98" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="98" spans="2:3">
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
     </row>
-    <row r="99" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="99" spans="2:3">
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
     </row>
-    <row r="100" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="100" spans="2:3">
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
     </row>
-    <row r="101" spans="2:3" x14ac:dyDescent="0.6">
+    <row r="101" spans="2:3">
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
     </row>
@@ -3498,14 +3550,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF141B82-E770-459A-B61E-AA19C7A0D3EE}">
   <dimension ref="A1:J6"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="2" max="2" width="12.5625" customWidth="1"/>
     <col min="3" max="3" width="9.25" style="18" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.5625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>131</v>
       </c>
@@ -3534,7 +3586,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>130</v>
       </c>
@@ -3566,12 +3618,12 @@
         <v>147</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>130</v>
       </c>
@@ -3597,12 +3649,12 @@
         <v>402</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>146</v>
       </c>
@@ -3644,19 +3696,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F5C2ECD-FC40-4B62-B0AC-B688596AF17A}">
   <dimension ref="A1:C128"/>
-  <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="11.5625" customWidth="1"/>
     <col min="2" max="2" width="20.25" customWidth="1"/>
     <col min="3" max="3" width="27.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="17.25" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:3" ht="17.25">
       <c r="A1" s="19" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="3" spans="1:3">
       <c r="A3" s="20" t="s">
         <v>152</v>
       </c>
@@ -3667,7 +3719,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:3">
       <c r="A4" s="21">
         <v>1</v>
       </c>
@@ -3678,7 +3730,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:3">
       <c r="A5" s="21">
         <v>2</v>
       </c>
@@ -3689,7 +3741,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="6" spans="1:3">
       <c r="A6" s="21">
         <v>3</v>
       </c>
@@ -3700,7 +3752,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="7" spans="1:3">
       <c r="A7" s="21">
         <v>4</v>
       </c>
@@ -3711,7 +3763,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="8" spans="1:3">
       <c r="A8" s="21">
         <v>5</v>
       </c>
@@ -3722,7 +3774,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="9" spans="1:3">
       <c r="A9" s="21">
         <v>6</v>
       </c>
@@ -3733,7 +3785,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="10" spans="1:3">
       <c r="A10" s="21">
         <v>7</v>
       </c>
@@ -3744,7 +3796,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="11" spans="1:3">
       <c r="A11" s="21">
         <v>8</v>
       </c>
@@ -3755,7 +3807,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="12" spans="1:3">
       <c r="A12" s="21">
         <v>9</v>
       </c>
@@ -3766,7 +3818,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="13" spans="1:3">
       <c r="A13" s="21">
         <v>10</v>
       </c>
@@ -3777,7 +3829,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="14" spans="1:3">
       <c r="A14" s="21">
         <v>11</v>
       </c>
@@ -3788,7 +3840,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:3">
       <c r="A15" s="21">
         <v>12</v>
       </c>
@@ -3799,7 +3851,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="16" spans="1:3">
       <c r="A16" s="21">
         <v>13</v>
       </c>
@@ -3810,7 +3862,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="17" spans="1:3">
       <c r="A17" s="21">
         <v>14</v>
       </c>
@@ -3821,7 +3873,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="18" spans="1:3">
       <c r="A18" s="21">
         <v>15</v>
       </c>
@@ -3832,7 +3884,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="19" spans="1:3">
       <c r="A19" s="21">
         <v>16</v>
       </c>
@@ -3843,7 +3895,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="20" spans="1:3" ht="27">
       <c r="A20" s="21">
         <v>17</v>
       </c>
@@ -3854,7 +3906,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="21" spans="1:3" ht="27">
       <c r="A21" s="21">
         <v>18</v>
       </c>
@@ -3865,7 +3917,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="22" spans="1:3" ht="27">
       <c r="A22" s="21">
         <v>19</v>
       </c>
@@ -3876,7 +3928,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="23" spans="1:3">
       <c r="A23" s="21">
         <v>20</v>
       </c>
@@ -3887,7 +3939,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="24" spans="1:3">
       <c r="A24" s="21">
         <v>21</v>
       </c>
@@ -3898,7 +3950,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="25" spans="1:3">
       <c r="A25" s="21">
         <v>22</v>
       </c>
@@ -3909,7 +3961,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="26" spans="1:3">
       <c r="A26" s="21">
         <v>23</v>
       </c>
@@ -3920,7 +3972,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="27" spans="1:3">
       <c r="A27" s="21">
         <v>24</v>
       </c>
@@ -3931,7 +3983,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="28" spans="1:3" ht="27">
       <c r="A28" s="21">
         <v>25</v>
       </c>
@@ -3942,7 +3994,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="29" spans="1:3">
       <c r="A29" s="21">
         <v>26</v>
       </c>
@@ -3953,7 +4005,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="30" spans="1:3">
       <c r="A30" s="21">
         <v>27</v>
       </c>
@@ -3964,7 +4016,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="31" spans="1:3" ht="27">
       <c r="A31" s="21">
         <v>28</v>
       </c>
@@ -3975,7 +4027,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="32" spans="1:3" ht="27">
       <c r="A32" s="21">
         <v>29</v>
       </c>
@@ -3986,7 +4038,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="33" spans="1:3" ht="27">
       <c r="A33" s="21">
         <v>30</v>
       </c>
@@ -3997,7 +4049,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="34" spans="1:3" ht="27">
       <c r="A34" s="21">
         <v>31</v>
       </c>
@@ -4008,7 +4060,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="35" spans="1:3">
       <c r="A35" s="21">
         <v>32</v>
       </c>
@@ -4019,7 +4071,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="36" spans="1:3" ht="27">
       <c r="A36" s="21">
         <v>33</v>
       </c>
@@ -4030,7 +4082,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="37" spans="1:3">
       <c r="A37" s="21">
         <v>34</v>
       </c>
@@ -4041,7 +4093,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="38" spans="1:3" ht="27">
       <c r="A38" s="21">
         <v>35</v>
       </c>
@@ -4052,7 +4104,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="39" spans="1:3" ht="27">
       <c r="A39" s="21">
         <v>36</v>
       </c>
@@ -4063,7 +4115,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="40" spans="1:3" ht="27">
       <c r="A40" s="21">
         <v>37</v>
       </c>
@@ -4074,7 +4126,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="41" spans="1:3">
       <c r="A41" s="21">
         <v>38</v>
       </c>
@@ -4085,7 +4137,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="42" spans="1:3">
       <c r="A42" s="21">
         <v>39</v>
       </c>
@@ -4096,7 +4148,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="43" spans="1:3">
       <c r="A43" s="21">
         <v>40</v>
       </c>
@@ -4107,7 +4159,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="44" spans="1:3">
       <c r="A44" s="21">
         <v>41</v>
       </c>
@@ -4118,7 +4170,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="45" spans="1:3">
       <c r="A45" s="21">
         <v>42</v>
       </c>
@@ -4129,7 +4181,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="46" spans="1:3" ht="27">
       <c r="A46" s="21">
         <v>43</v>
       </c>
@@ -4140,7 +4192,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="47" spans="1:3">
       <c r="A47" s="21">
         <v>44</v>
       </c>
@@ -4151,7 +4203,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="48" spans="1:3">
       <c r="A48" s="21">
         <v>45</v>
       </c>
@@ -4162,7 +4214,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="49" spans="1:3">
       <c r="A49" s="21">
         <v>46</v>
       </c>
@@ -4173,7 +4225,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="50" spans="1:3">
       <c r="A50" s="21">
         <v>47</v>
       </c>
@@ -4184,7 +4236,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="51" spans="1:3">
       <c r="A51" s="21">
         <v>48</v>
       </c>
@@ -4195,7 +4247,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="52" spans="1:3">
       <c r="A52" s="21">
         <v>49</v>
       </c>
@@ -4206,7 +4258,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="53" spans="1:3">
       <c r="A53" s="21">
         <v>50</v>
       </c>
@@ -4217,7 +4269,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="54" spans="1:3">
       <c r="A54" s="21">
         <v>51</v>
       </c>
@@ -4228,7 +4280,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="55" spans="1:3">
       <c r="A55" s="21">
         <v>52</v>
       </c>
@@ -4239,7 +4291,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="56" spans="1:3">
       <c r="A56" s="21">
         <v>53</v>
       </c>
@@ -4250,7 +4302,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="57" spans="1:3">
       <c r="A57" s="21">
         <v>54</v>
       </c>
@@ -4261,7 +4313,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="58" spans="1:3">
       <c r="A58" s="21">
         <v>55</v>
       </c>
@@ -4272,7 +4324,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="59" spans="1:3">
       <c r="A59" s="21">
         <v>56</v>
       </c>
@@ -4283,7 +4335,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="60" spans="1:3">
       <c r="A60" s="21">
         <v>57</v>
       </c>
@@ -4294,7 +4346,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="61" spans="1:3">
       <c r="A61" s="21">
         <v>58</v>
       </c>
@@ -4305,7 +4357,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="62" spans="1:3">
       <c r="A62" s="21">
         <v>59</v>
       </c>
@@ -4316,7 +4368,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="63" spans="1:3">
       <c r="A63" s="21">
         <v>60</v>
       </c>
@@ -4327,7 +4379,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="64" spans="1:3" ht="27">
       <c r="A64" s="21">
         <v>61</v>
       </c>
@@ -4338,7 +4390,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="65" spans="1:3" ht="27">
       <c r="A65" s="21">
         <v>62</v>
       </c>
@@ -4349,7 +4401,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="66" spans="1:3" ht="27">
       <c r="A66" s="21">
         <v>63</v>
       </c>
@@ -4360,7 +4412,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="67" spans="1:3">
       <c r="A67" s="21">
         <v>64</v>
       </c>
@@ -4371,7 +4423,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="68" spans="1:3">
       <c r="A68" s="21">
         <v>65</v>
       </c>
@@ -4382,7 +4434,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="69" spans="1:3">
       <c r="A69" s="21">
         <v>66</v>
       </c>
@@ -4393,7 +4445,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="70" spans="1:3">
       <c r="A70" s="21">
         <v>67</v>
       </c>
@@ -4404,7 +4456,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="71" spans="1:3">
       <c r="A71" s="21">
         <v>68</v>
       </c>
@@ -4415,7 +4467,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="72" spans="1:3" ht="27">
       <c r="A72" s="21">
         <v>69</v>
       </c>
@@ -4426,7 +4478,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="73" spans="1:3" ht="27">
       <c r="A73" s="21">
         <v>70</v>
       </c>
@@ -4437,7 +4489,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="74" spans="1:3" ht="27">
       <c r="A74" s="21">
         <v>71</v>
       </c>
@@ -4448,7 +4500,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="75" spans="1:3" ht="27">
       <c r="A75" s="21">
         <v>72</v>
       </c>
@@ -4459,7 +4511,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="76" spans="1:3" ht="27">
       <c r="A76" s="21">
         <v>73</v>
       </c>
@@ -4470,7 +4522,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="77" spans="1:3">
       <c r="A77" s="21">
         <v>74</v>
       </c>
@@ -4481,7 +4533,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="78" spans="1:3" ht="27">
       <c r="A78" s="21">
         <v>75</v>
       </c>
@@ -4492,7 +4544,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="79" spans="1:3">
       <c r="A79" s="21">
         <v>76</v>
       </c>
@@ -4503,7 +4555,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="80" spans="1:3">
       <c r="A80" s="21">
         <v>77</v>
       </c>
@@ -4514,7 +4566,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="81" spans="1:3">
       <c r="A81" s="21">
         <v>78</v>
       </c>
@@ -4525,7 +4577,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="82" spans="1:3" ht="27">
       <c r="A82" s="21">
         <v>79</v>
       </c>
@@ -4536,7 +4588,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="83" spans="1:3">
       <c r="A83" s="21">
         <v>80</v>
       </c>
@@ -4547,7 +4599,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="84" spans="1:3">
       <c r="A84" s="21">
         <v>81</v>
       </c>
@@ -4558,7 +4610,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="85" spans="1:3" ht="27">
       <c r="A85" s="21">
         <v>82</v>
       </c>
@@ -4569,7 +4621,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="86" spans="1:3">
       <c r="A86" s="21">
         <v>83</v>
       </c>
@@ -4580,7 +4632,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="87" spans="1:3">
       <c r="A87" s="21">
         <v>84</v>
       </c>
@@ -4591,7 +4643,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="88" spans="1:3">
       <c r="A88" s="21">
         <v>85</v>
       </c>
@@ -4602,7 +4654,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="89" spans="1:3">
       <c r="A89" s="21">
         <v>86</v>
       </c>
@@ -4613,7 +4665,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="90" spans="1:3">
       <c r="A90" s="21">
         <v>87</v>
       </c>
@@ -4624,7 +4676,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="91" spans="1:3">
       <c r="A91" s="21">
         <v>88</v>
       </c>
@@ -4635,7 +4687,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="92" spans="1:3" ht="27">
       <c r="A92" s="21">
         <v>89</v>
       </c>
@@ -4646,7 +4698,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="93" spans="1:3" ht="27">
       <c r="A93" s="21">
         <v>90</v>
       </c>
@@ -4657,7 +4709,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="94" spans="1:3" ht="27">
       <c r="A94" s="21">
         <v>91</v>
       </c>
@@ -4668,7 +4720,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="95" spans="1:3">
       <c r="A95" s="21">
         <v>92</v>
       </c>
@@ -4679,7 +4731,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="96" spans="1:3">
       <c r="A96" s="21">
         <v>93</v>
       </c>
@@ -4690,7 +4742,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="97" spans="1:3" ht="27">
       <c r="A97" s="21">
         <v>94</v>
       </c>
@@ -4701,7 +4753,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="98" spans="1:3">
       <c r="A98" s="21">
         <v>95</v>
       </c>
@@ -4712,7 +4764,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="99" spans="1:3">
       <c r="A99" s="21">
         <v>96</v>
       </c>
@@ -4723,7 +4775,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="100" spans="1:3">
       <c r="A100" s="21">
         <v>97</v>
       </c>
@@ -4734,7 +4786,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="101" spans="1:3">
       <c r="A101" s="21">
         <v>98</v>
       </c>
@@ -4745,7 +4797,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="102" spans="1:3">
       <c r="A102" s="21">
         <v>99</v>
       </c>
@@ -4756,7 +4808,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="103" spans="1:3" ht="27">
       <c r="A103" s="21">
         <v>100</v>
       </c>
@@ -4767,7 +4819,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="104" spans="1:3">
       <c r="A104" s="21">
         <v>101</v>
       </c>
@@ -4778,7 +4830,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="105" spans="1:3">
       <c r="A105" s="21">
         <v>102</v>
       </c>
@@ -4789,7 +4841,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="106" spans="1:3">
       <c r="A106" s="21">
         <v>103</v>
       </c>
@@ -4800,7 +4852,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="107" spans="1:3">
       <c r="A107" s="21">
         <v>104</v>
       </c>
@@ -4811,7 +4863,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="108" spans="1:3">
       <c r="A108" s="21">
         <v>105</v>
       </c>
@@ -4822,7 +4874,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="27" x14ac:dyDescent="0.6">
+    <row r="109" spans="1:3" ht="27">
       <c r="A109" s="21">
         <v>106</v>
       </c>
@@ -4833,7 +4885,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="110" spans="1:3">
       <c r="A110" s="21">
         <v>107</v>
       </c>
@@ -4844,7 +4896,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="111" spans="1:3">
       <c r="A111" s="21">
         <v>108</v>
       </c>
@@ -4855,7 +4907,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="112" spans="1:3">
       <c r="A112" s="21">
         <v>109</v>
       </c>
@@ -4866,7 +4918,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="113" spans="1:3">
       <c r="A113" s="21">
         <v>110</v>
       </c>
@@ -4877,7 +4929,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="114" spans="1:3">
       <c r="A114" s="21">
         <v>111</v>
       </c>
@@ -4888,7 +4940,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="115" spans="1:3">
       <c r="A115" s="21">
         <v>112</v>
       </c>
@@ -4899,7 +4951,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="116" spans="1:3">
       <c r="A116" s="21">
         <v>113</v>
       </c>
@@ -4910,7 +4962,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="117" spans="1:3">
       <c r="A117" s="21">
         <v>114</v>
       </c>
@@ -4921,7 +4973,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="118" spans="1:3">
       <c r="A118" s="21">
         <v>115</v>
       </c>
@@ -4932,7 +4984,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="119" spans="1:3">
       <c r="A119" s="21">
         <v>116</v>
       </c>
@@ -4943,7 +4995,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="120" spans="1:3">
       <c r="A120" s="21">
         <v>117</v>
       </c>
@@ -4954,7 +5006,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="121" spans="1:3">
       <c r="A121" s="21">
         <v>118</v>
       </c>
@@ -4965,7 +5017,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="122" spans="1:3">
       <c r="A122" s="21">
         <v>119</v>
       </c>
@@ -4976,7 +5028,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="123" spans="1:3">
       <c r="A123" s="21">
         <v>120</v>
       </c>
@@ -4987,7 +5039,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="124" spans="1:3">
       <c r="A124" s="21">
         <v>121</v>
       </c>
@@ -4998,7 +5050,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="125" spans="1:3">
       <c r="A125" s="21">
         <v>122</v>
       </c>
@@ -5009,7 +5061,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="126" spans="1:3">
       <c r="A126" s="21">
         <v>123</v>
       </c>
@@ -5020,7 +5072,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="127" spans="1:3">
       <c r="A127" s="21">
         <v>124</v>
       </c>
@@ -5031,7 +5083,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.6">
+    <row r="128" spans="1:3">
       <c r="A128" s="21">
         <v>125</v>
       </c>

--- a/knto_images(현황).xlsx
+++ b/knto_images(현황).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\code\WebImages_travel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18A17089-4E6A-436C-A492-A20A667B4C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8ABF02-AFEA-4DDE-8A30-8A1303F20608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4470" yWindow="660" windowWidth="14310" windowHeight="12120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="422">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="434">
   <si>
     <t>여행지명</t>
   </si>
@@ -1480,12 +1480,153 @@
   <si>
     <t>한강드론공원</t>
   </si>
+  <si>
+    <t>🌿 여의도한강공원</t>
+  </si>
+  <si>
+    <t>🌳 뚝섬한강공원</t>
+  </si>
+  <si>
+    <t>🚁 한강드론공원</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 여의도한강공원 봄 피크닉 완벽 가이드 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🌸</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 벚꽃·야경·데이트 코스 총정리</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3. 여의도한강공원:한강 야경 끝판왕! 여의도한강공원 밤 산책 코스 &amp; 인생사진 스팟 추천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 여의도한강공원:서울 도심 속 힐링 명소, 여의도한강공원 즐기는 7가지 방법 (자전거·치맥·산책)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 뚝섬한강공원: 뚝섬한강공원 나들이 추천 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>💚</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 피크닉·수영장·자전거 코스 한 번에 즐기기</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뚝섬한강공원: 서울 여름 필수 코스! 뚝섬한강공원 수영장부터 데이트 코스까지 완벽 정리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>뚝섬한강공원:  감성 피크닉 성지, 뚝섬한강공원에서 하루 보내는 법 (준비물·꿀팁 포함)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. 한강드론공원: 한강드론공원 완벽 가이드 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🚀</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 드론 초보부터 촬영 명소까지 총정리</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한강드론공원: 서울에서 드론 날리기 좋은 곳! 한강드론공원 이용방법·주의사항 정리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">한강드론공원: 이색 취미 추천 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Emoji"/>
+        <family val="2"/>
+      </rPr>
+      <t>🎮</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 한강드론공원에서 즐기는 드론 비행 체험기</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1592,6 +1733,13 @@
       <name val="Pretendard GOV"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Emoji"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -1649,7 +1797,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1725,6 +1873,9 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2868,7 +3019,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64F05010-FAED-41D9-AC86-A7A9CDE8E2F2}">
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -3397,123 +3548,162 @@
       <c r="B66" s="2"/>
       <c r="C66" s="2"/>
     </row>
-    <row r="67" spans="2:6">
+    <row r="67" spans="2:6" ht="27">
       <c r="B67" s="2"/>
       <c r="C67" s="2"/>
+      <c r="F67" s="13" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="68" spans="2:6">
       <c r="B68" s="2"/>
       <c r="C68" s="2"/>
+      <c r="F68" s="14"/>
     </row>
     <row r="69" spans="2:6">
       <c r="B69" s="2"/>
       <c r="C69" s="2"/>
+      <c r="F69" s="23" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="70" spans="2:6">
       <c r="B70" s="2"/>
       <c r="C70" s="2"/>
+      <c r="F70" s="23" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="71" spans="2:6">
       <c r="B71" s="2"/>
       <c r="C71" s="2"/>
-    </row>
-    <row r="72" spans="2:6">
+      <c r="F71" s="23" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="72" spans="2:6" ht="27">
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
+      <c r="F72" s="13" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="73" spans="2:6">
       <c r="B73" s="2"/>
       <c r="C73" s="2"/>
+      <c r="F73" s="14"/>
     </row>
     <row r="74" spans="2:6">
       <c r="B74" s="2"/>
       <c r="C74" s="2"/>
+      <c r="F74" s="34" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="75" spans="2:6">
       <c r="B75" s="2"/>
       <c r="C75" s="2"/>
+      <c r="F75" s="34" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="76" spans="2:6">
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
-    </row>
-    <row r="77" spans="2:6">
+      <c r="F76" s="34" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" ht="27">
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
+      <c r="F77" s="13" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="78" spans="2:6">
       <c r="B78" s="2"/>
       <c r="C78" s="2"/>
+      <c r="F78" s="14"/>
     </row>
     <row r="79" spans="2:6">
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
+      <c r="F79" s="34" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="80" spans="2:6">
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
-    </row>
-    <row r="81" spans="2:3">
+      <c r="F80" s="34" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="81" spans="2:6">
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
-    </row>
-    <row r="82" spans="2:3">
+      <c r="F81" s="34" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="82" spans="2:6">
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="2:3">
+    <row r="83" spans="2:6">
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="2:3">
+    <row r="84" spans="2:6">
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="2:3">
+    <row r="85" spans="2:6">
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="2:3">
+    <row r="86" spans="2:6">
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="2:3">
+    <row r="87" spans="2:6">
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="2:3">
+    <row r="88" spans="2:6">
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
     </row>
-    <row r="89" spans="2:3">
+    <row r="89" spans="2:6">
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
     </row>
-    <row r="90" spans="2:3">
+    <row r="90" spans="2:6">
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="2:3">
+    <row r="91" spans="2:6">
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
     </row>
-    <row r="92" spans="2:3">
+    <row r="92" spans="2:6">
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
     </row>
-    <row r="93" spans="2:3">
+    <row r="93" spans="2:6">
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
     </row>
-    <row r="94" spans="2:3">
+    <row r="94" spans="2:6">
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
     </row>
-    <row r="95" spans="2:3">
+    <row r="95" spans="2:6">
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
     </row>
-    <row r="96" spans="2:3">
+    <row r="96" spans="2:6">
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
     </row>
@@ -3525,21 +3715,9 @@
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
     </row>
-    <row r="99" spans="2:3">
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-    </row>
-    <row r="100" spans="2:3">
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-    </row>
-    <row r="101" spans="2:3">
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F1:F89">
-    <sortCondition ref="F1:F89"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="F1:F86">
+    <sortCondition ref="F1:F86"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
